--- a/naver-place-crawler/results_nail/달성군_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/달성군_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V103"/>
+  <dimension ref="A1:V104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,20 +564,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>현네일앤뷰티</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>lovelyddu1@naver.com</t>
-        </is>
-      </c>
+          <t>홀드풋케어 발톱무좀 내성발톱 문제성발관리</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>070-4866-1122</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 인흥길 83 1층</t>
+          <t>대구광역시 달성군 유가읍 테크노북로 260 201동 2200호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -632,17 +632,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1094979616</t>
+          <t>1280044307</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1094979616</t>
+          <t>https://m.place.naver.com/place/1280044307</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -654,29 +654,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>네일데이</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>honey126@naver.com</t>
-        </is>
-      </c>
+          <t>모인뷰티</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1385-4658</t>
+          <t>0507-1374-7011</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 대실역북로4길 6 1층</t>
+          <t>대구광역시 달성군 화원읍 화원로1길 46-8 1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/https://www.instagram.com/nail_day_k?igsh=eGpma3JucTN6Ymp4</t>
+          <t>https://www.instagram.com/moin_beauty</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -711,13 +707,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,17 +722,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1302571156</t>
+          <t>1855496054</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1302571156</t>
+          <t>https://m.place.naver.com/place/1855496054</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -748,12 +744,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>벨라부띠끄</t>
+          <t>네일은 맑음</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>y77777k@naver.com</t>
+          <t>kkje38317@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -761,7 +757,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로 874 벨라부띠끄</t>
+          <t>대구광역시 달성군 현풍읍 테크노상업로2길 7-12 2층 204호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -797,17 +793,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -816,17 +812,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1192828282</t>
+          <t>1395910390</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1192828282</t>
+          <t>https://m.place.naver.com/place/1395910390</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -838,20 +834,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일&amp;스킨</t>
+          <t>네일누림 현풍테크노폴리스점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>feel3051@naver.com</t>
+          <t>chelba789@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1489-4282</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 화원로7길 54</t>
+          <t>대구광역시 달성군 유가읍 테크노상업로 111 테크노폴리스4단지 상가동 1층 105호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -891,13 +891,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -906,17 +906,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>38401077</t>
+          <t>1028594389</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38401077</t>
+          <t>https://m.place.naver.com/place/1028594389</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -928,34 +928,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>부베니르 네일</t>
+          <t>비네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>vb_nail@naver.com</t>
+          <t>eunbi1202@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1414-4481</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 화암로 69 명곡시장 안 할매국밥 옆쪽</t>
+          <t>대구광역시 달성군 다사읍 서재로 96-1 1층 비네일</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://toss.place/_lb/jYywkSBMS</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -970,14 +966,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5y7c4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -989,13 +981,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>525</v>
+        <v>21</v>
       </c>
       <c r="Q6" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="R6" t="n">
-        <v>571</v>
+        <v>54</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,17 +996,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1474593561</t>
+          <t>36060602</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1474593561</t>
+          <t>https://m.place.naver.com/place/36060602</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1026,24 +1018,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>으니네일</t>
+          <t>반짝반짝네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>gost5544@naver.com</t>
+          <t>dkw05026@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1385-1093</t>
+          <t>053-581-0210</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로174길 21 2층</t>
+          <t>대구광역시 달성군 다사읍 서재본길 10 1층 101호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1079,17 +1071,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,17 +1090,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1662155594</t>
+          <t>1571722665</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1662155594</t>
+          <t>https://m.place.naver.com/place/1571722665</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1120,24 +1112,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>제이뷰티</t>
+          <t>네일 봄</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nanamoon23@naver.com</t>
+          <t>joolijooli@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1384-1216</t>
+          <t>0507-1306-6012</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 구지면 국가산단대로70길 42 상가 1호</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로 875 MA프라자 105호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1173,17 +1165,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
         <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,17 +1184,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1507035488</t>
+          <t>1419253509</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1507035488</t>
+          <t>https://m.place.naver.com/place/1419253509</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1214,24 +1206,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>겸,네일</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>qkrdbsgp55@naver.com</t>
-        </is>
-      </c>
+          <t>현네일앤뷰티</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1442-0376</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노상업로 108 205호</t>
+          <t>대구광역시 달성군 화원읍 인흥길 83 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1271,13 +1255,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,17 +1270,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1747951212</t>
+          <t>1094979616</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1747951212</t>
+          <t>https://m.place.naver.com/place/1094979616</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1308,29 +1292,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일스토리</t>
+          <t>미유네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>yeju0414@naver.com</t>
+          <t>atsing427@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>053-585-3646</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 서재로7길 25 동화아이위시 3차 상가 2층 601동 203호</t>
+          <t>대구광역시 달성군 현풍읍 테크노상업로 34 1층 리차드헤어샵 안</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/miyou_nail2023</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1340,7 +1320,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1361,17 +1341,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,17 +1360,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>36208505</t>
+          <t>1953875264</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36208505</t>
+          <t>https://m.place.naver.com/place/1953875264</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1402,29 +1382,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>더착한네일</t>
+          <t>호네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>chamhanjh@naver.com</t>
+          <t>hhhong88@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1322-1416</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 죽곡1길 19 나비타워 1층 104호 더착한네일</t>
+          <t>대구광역시 달성군 다사읍 서재로12길 38 에코폴리스 동화아이위시 1차상가 호네일</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/ho_nail0999</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1434,7 +1410,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1450,7 +1426,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1459,13 +1435,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,17 +1450,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1595935829</t>
+          <t>1248903128</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1595935829</t>
+          <t>https://m.place.naver.com/place/1248903128</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1496,25 +1472,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>미유네일</t>
+          <t>수이네일 다사대실역점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>cute8226@naver.com</t>
+          <t>sweets0101@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1423-4145</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노상업로 34 1층 리차드헤어샵 안</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로174길 50 죽곡협성휴포레 상가 301동 105호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/sui.nail.shop</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1524,7 +1504,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1549,13 +1529,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1564,17 +1544,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1953875264</t>
+          <t>1939839368</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1953875264</t>
+          <t>https://m.place.naver.com/place/1939839368</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1586,39 +1566,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>제이오뷰티 다사대실역점</t>
+          <t>레비라네일 현풍테크노폴리스점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>happy_y119@naver.com</t>
+          <t>apple6931@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1372-0952</t>
+          <t>0507-1430-5033</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로 846-1 제이오뷰티</t>
+          <t>대구광역시 달성군 유가읍 테크노북로 260 예미지상가 2171호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_YJxhxlG</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1628,14 +1608,10 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4a6zl</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>O</t>
@@ -1647,13 +1623,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="Q13" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>42</v>
+        <v>159</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,17 +1638,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1940949870</t>
+          <t>1808169841</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1940949870</t>
+          <t>https://m.place.naver.com/place/1808169841</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1684,29 +1660,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>네일,또만나</t>
+          <t>유닉네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>deepgriep29@naver.com</t>
+          <t>bdt9947@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1356-9059</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 구지면 국가산단북로60길 66 1층 103호</t>
+          <t>대구광역시 달성군 현풍읍 현풍중앙로 46-1 1층 유닉네일</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/u__nik.nail</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1716,7 +1688,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1741,13 +1713,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,17 +1728,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2071071912</t>
+          <t>1621081877</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2071071912</t>
+          <t>https://m.place.naver.com/place/1621081877</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1778,29 +1750,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>모브네일</t>
+          <t>오늘도네일</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>jaera423@naver.com</t>
+          <t>j2lang@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1327-7428</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 구지면 국가산단대로70길 17 대구국가산단디에트르더센트럴 상가 111호</t>
+          <t>대구광역시 달성군 구지면 과학마을로3길 15 1층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/oneuldo__nail/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1810,7 +1778,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1831,18 +1799,18 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
+        <v>4</v>
+      </c>
+      <c r="R15" t="n">
         <v>5</v>
       </c>
-      <c r="R15" t="n">
-        <v>8</v>
-      </c>
       <c r="S15" t="inlineStr">
         <is>
           <t>X</t>
@@ -1850,17 +1818,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1135244635</t>
+          <t>1331774074</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1135244635</t>
+          <t>https://m.place.naver.com/place/1331774074</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1872,24 +1840,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>네일하담</t>
+          <t>네일샵</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mementomori-24@naver.com</t>
+          <t>bitna0614@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1318-5676</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 논공읍 논공로9길 68 2층</t>
+          <t>대구광역시 달성군 화원읍 화원로 29</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1925,17 +1889,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,17 +1908,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1157430781</t>
+          <t>1210929171</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1157430781</t>
+          <t>https://m.place.naver.com/place/1210929171</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1966,29 +1930,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>혜진뷰티</t>
+          <t>예쁘제네일뷰티</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>jjin88035@naver.com</t>
+          <t>shimaroma@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1306-5661</t>
+          <t>0507-1330-4637</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 화원로2길 13 1층</t>
+          <t>대구광역시 달성군 구지면 과학마을로2길 6 상가1층 예쁘제</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/nail_yeppeuje</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1998,7 +1962,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2019,17 +1983,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2038,17 +2002,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1025452354</t>
+          <t>1482366649</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1025452354</t>
+          <t>https://m.place.naver.com/place/1482366649</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2060,24 +2024,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>홀드풋케어 발톱무좀 내성발톱 문제성발관리</t>
+          <t>꾸밈네일</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>bi1142@naver.com</t>
+          <t>smileahj@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>070-4866-1122</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노북로 260 201동 2200호</t>
+          <t>대구광역시 달성군 다사읍 서재로30길 17 보성1차상가 101호 꾸밈네일</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2117,13 +2077,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="R18" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2132,17 +2092,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1280044307</t>
+          <t>706872304</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1280044307</t>
+          <t>https://m.place.naver.com/place/706872304</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2154,25 +2114,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>네일 예쁘다</t>
+          <t>네일써니</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>yooky617@naver.com</t>
+          <t>ha780106@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1410-7991</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노상업로 108 2층 205호 네일예쁘다</t>
+          <t>대구광역시 달성군 화원읍 비슬로 2545 상가 110동 3층 310호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail.sunny7985</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2182,7 +2146,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2203,17 +2167,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R19" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2222,17 +2186,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1252953982</t>
+          <t>1704201083</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1252953982</t>
+          <t>https://m.place.naver.com/place/1704201083</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2244,25 +2208,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>네일채움</t>
+          <t>썸네일 대구다사점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>heeya6782@naver.com</t>
+          <t>yooywyooyw@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1331-7260</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 대실역북로 66-1 네일채움</t>
+          <t>대구광역시 달성군 다사읍 대실역북로5길 54-18 1층 101호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/so.me_nail</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2272,7 +2240,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2297,13 +2265,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>5</v>
+        <v>195</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="R20" t="n">
-        <v>9</v>
+        <v>213</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2312,17 +2280,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1840386729</t>
+          <t>1932038368</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1840386729</t>
+          <t>https://m.place.naver.com/place/1932038368</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2334,29 +2302,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>예쁘제네일뷰티</t>
+          <t>네일을,이쁘게</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>shimaroma@naver.com</t>
+          <t>loosetime@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1330-4637</t>
+          <t>0507-1317-3565</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 구지면 과학마을로2길 6 상가1층 예쁘제</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로 881 1층.107호 네일은,이쁘게</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_yeppeuje</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2366,7 +2334,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2387,17 +2355,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2406,17 +2374,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1482366649</t>
+          <t>1456297687</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1482366649</t>
+          <t>https://m.place.naver.com/place/1456297687</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2428,29 +2396,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>지니네일</t>
+          <t>뮤아드네일</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>goto_seoul@naver.com</t>
+          <t>twolee10_@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1389-4020</t>
+          <t>0507-1312-2226</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 옥포읍 비슬로447길 11 달성삼환나우빌 301동 102호</t>
+          <t>대구광역시 달성군 현풍읍 테크노중앙대로5길 15-9 1층 101호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/muad.nail</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2460,7 +2428,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2481,17 +2449,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2500,17 +2468,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1621609186</t>
+          <t>2002612318</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1621609186</t>
+          <t>https://m.place.naver.com/place/2002612318</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2522,12 +2490,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>네일을, 이쁘게</t>
+          <t>네일&amp;스킨</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>gold77com@naver.com</t>
+          <t>feel3051@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -2535,12 +2503,12 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로 881 1층 107호</t>
+          <t>대구광역시 달성군 화원읍 화원로7길 54</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pretty_nai1_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2550,7 +2518,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2571,18 +2539,18 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>160</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
         <v>2</v>
       </c>
-      <c r="R23" t="n">
-        <v>162</v>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>X</t>
@@ -2590,17 +2558,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1822297833</t>
+          <t>38401077</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1822297833</t>
+          <t>https://m.place.naver.com/place/38401077</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2612,29 +2580,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>네일 봄</t>
+          <t>으니네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>joolijooli@naver.com</t>
+          <t>gost5544@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1306-6012</t>
+          <t>0507-1385-1093</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로 875 MA프라자 105호</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로174길 21 2층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/euni__nail</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2644,7 +2612,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2665,17 +2633,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2684,17 +2652,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1419253509</t>
+          <t>1662155594</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1419253509</t>
+          <t>https://m.place.naver.com/place/1662155594</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2706,29 +2674,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>다섯손꾸락네일</t>
+          <t>욜로네일</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dongee_where@naver.com</t>
+          <t>s2s20228@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0507-1344-3247</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로174길 50 301동 지하2층 A102 호</t>
+          <t>대구광역시 달성군 옥포읍 돌미로2길 6</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/yolonail9010</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2738,7 +2702,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2763,13 +2727,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2778,17 +2742,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1967769482</t>
+          <t>1935910413</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1967769482</t>
+          <t>https://m.place.naver.com/place/1935910413</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2800,25 +2764,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>네일티라노 현풍</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>네일하담</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>mementomori-24@naver.com</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1364-3106</t>
+          <t>0507-1318-5676</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노중앙대로 240 한라하우젠트 상가 1층 120호</t>
+          <t>대구광역시 달성군 논공읍 논공로9길 68 2층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailhadam_</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2828,7 +2796,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2838,17 +2806,13 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4pk98</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2857,13 +2821,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>151</v>
+        <v>1</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2872,17 +2836,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1340647385</t>
+          <t>1157430781</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1340647385</t>
+          <t>https://m.place.naver.com/place/1157430781</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2894,29 +2858,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>엄지공주뷰티샵</t>
+          <t>뷰티해요</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>tosemdnlcl@naver.com</t>
+          <t>bonita5332@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1358-0830</t>
+          <t>0507-1336-7045</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 명곡로 9 명곡미래빌1단지 상가 2층</t>
+          <t>대구광역시 달성군 다사읍 대실역북로 12 301호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tosemdnlcl</t>
+          <t>https://blog.naver.com/bonita5332</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2951,13 +2915,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Q27" t="n">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="R27" t="n">
-        <v>97</v>
+        <v>176</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2966,17 +2930,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>20061778</t>
+          <t>1243747619</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20061778</t>
+          <t>https://m.place.naver.com/place/1243747619</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2988,25 +2952,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>루미네일</t>
+          <t>블리스네일</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jine_blog@naver.com</t>
+          <t>lee0ja8850@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1358-3759</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 옥포읍 돌미상업로2길 26 1층 루미네일</t>
+          <t>대구광역시 달성군 옥포읍 돌미로 70 대성베르힐 4단지 동문상가 3층 303호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lume._.nailllll</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3016,7 +2984,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3037,17 +3005,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="Q28" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="R28" t="n">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3056,17 +3024,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2070020547</t>
+          <t>1427642953</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2070020547</t>
+          <t>https://m.place.naver.com/place/1427642953</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3078,29 +3046,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>룩네일</t>
+          <t>네일채움</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>with_ivory@naver.com</t>
+          <t>rhdwnsla5656@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0507-1307-5776</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 옥포읍 돌미로 50 2층 201호</t>
+          <t>대구광역시 달성군 다사읍 대실역북로 66-1 네일채움</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>http://instagram.com/Lo_oknail</t>
+          <t>http://instagram.com/jj_ chaewoom</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3135,13 +3099,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3150,17 +3114,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1257117862</t>
+          <t>1840386729</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1257117862</t>
+          <t>https://m.place.naver.com/place/1840386729</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3172,25 +3136,25 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>뷰티플랏</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>스페이스 블링</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>mong_s_0810@naver.com</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0507-1333-4551</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 구지면 과학마을로 51-1 뷰티플랏</t>
+          <t>대구광역시 달성군 유가읍 테크노북로 260 2층 2164호(예미지 상가)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://instagram.com/beauty_plot</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3200,7 +3164,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3221,17 +3185,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>16</v>
+        <v>175</v>
       </c>
       <c r="Q30" t="n">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="R30" t="n">
-        <v>33</v>
+        <v>232</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3240,17 +3204,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1623449679</t>
+          <t>2080831582</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1623449679</t>
+          <t>https://m.place.naver.com/place/2080831582</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3262,29 +3226,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>오늘네일 다사대실점</t>
+          <t>혜진뷰티</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>wlsk203@naver.com</t>
+          <t>jjin88035@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1480-2662</t>
+          <t>0507-1306-5661</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 대실역북로 70 1층 오늘네일</t>
+          <t>대구광역시 달성군 화원읍 화원로2길 13 1층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oneul_nail80</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3294,7 +3258,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3315,17 +3279,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>169</v>
+        <v>89</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="R31" t="n">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3334,17 +3298,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1867576541</t>
+          <t>1025452354</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1867576541</t>
+          <t>https://m.place.naver.com/place/1025452354</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3356,29 +3320,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>맘스네일 현풍점</t>
+          <t>겸,네일</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>j_hee_2@naver.com</t>
+          <t>mneilacademy@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1334-7625</t>
+          <t>0507-1442-0376</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노중앙대로 326-27 1층</t>
+          <t>대구광역시 달성군 유가읍 테크노상업로 108 205호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hyunpung_momsnail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3388,7 +3352,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3409,17 +3373,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3428,17 +3392,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1058493414</t>
+          <t>1747951212</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1058493414</t>
+          <t>https://m.place.naver.com/place/1747951212</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3450,29 +3414,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>심쿵뷰티</t>
+          <t>더착한네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>pselll@naver.com</t>
+          <t>chamhanjh@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1356-4777</t>
+          <t>0507-1322-1416</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노북로 260 애비뉴스완상가 1103호</t>
+          <t>대구광역시 달성군 다사읍 죽곡1길 19 나비타워 1층 104호 더착한네일</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://instagram.com/the_kind_nail_1</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3482,7 +3446,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3503,17 +3467,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="R33" t="n">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3522,17 +3486,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1422631134</t>
+          <t>1595935829</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1422631134</t>
+          <t>https://m.place.naver.com/place/1595935829</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3544,21 +3508,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>네일헤몬 대구다사점</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>네일, The 예쁨</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>5haveagoodday@naver.com</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1493-0919</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 대실역북로 55 동화아이위시상가 301동103호</t>
+          <t>대구광역시 달성군 다사읍 매곡로12길 26 1층 106호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailhemon_dasa</t>
+          <t>https://www.instagram.com/nailtheyebbeum_dasa</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3593,13 +3565,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="Q34" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3608,17 +3580,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1440312692</t>
+          <t>1004489689</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1440312692</t>
+          <t>https://m.place.naver.com/place/1004489689</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3630,29 +3602,25 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>솜솜네일</t>
+          <t>네일하이</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>mydbfla33@naver.com</t>
+          <t>dojulie@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0507-1384-9259</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 현풍로47길 67 화이트캐슬 101호</t>
+          <t>대구광역시 달성군 현풍읍 테크노북로 33-5 1층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/somsom.nail2</t>
+          <t>https://www.instagram.com/nailhigh2021</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3687,13 +3655,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="R35" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3702,17 +3670,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1791561455</t>
+          <t>1919866561</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1791561455</t>
+          <t>https://m.place.naver.com/place/1919866561</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3724,34 +3692,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>진네일</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>jin_nail6453@naver.com</t>
-        </is>
-      </c>
+          <t>Nail,On</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1333-6453</t>
+          <t>0507-1446-3385</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노공원로 17 벨류스퀘어1층113호 진네일</t>
+          <t>대구광역시 달성군 구지면 과학마을로5길 45 1층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jin_nail6453</t>
+          <t>https://www.instagram.com/nail.on__</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3761,7 +3725,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3781,13 +3745,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="Q36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R36" t="n">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3796,17 +3760,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1289979524</t>
+          <t>2080619879</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1289979524</t>
+          <t>https://m.place.naver.com/place/2080619879</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3818,29 +3782,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>네일리영</t>
+          <t>더고은네일 대구화원점</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2090063@naver.com</t>
+          <t>thegoeunnail@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1375-4992</t>
+          <t>0507-1380-6762</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노상업로 68 센텀타워1층 후면 네일리영</t>
+          <t>대구광역시 달성군 화원읍 비슬로 2545 화원이진캐스빌상가 110동 2층 220호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naily_yeong</t>
+          <t>https://blog.naver.com/thegoeunnail</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3855,7 +3819,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3866,7 +3830,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3875,13 +3839,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>42</v>
+        <v>697</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="R37" t="n">
-        <v>47</v>
+        <v>748</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3890,17 +3854,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1456853511</t>
+          <t>1283196595</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1456853511</t>
+          <t>https://m.place.naver.com/place/1283196595</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3912,25 +3876,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>호네일</t>
+          <t>다섯손꾸락네일</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>hhhong88@naver.com</t>
+          <t>dongee_where@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1344-3247</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 서재로12길 38 에코폴리스 동화아이위시 1차상가 호네일</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로174길 50 301동 지하2층 A102 호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ho_nail0999</t>
+          <t>https://www.instagram.com/5ive_fingers_</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3956,7 +3924,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3965,13 +3933,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3980,17 +3948,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1248903128</t>
+          <t>1967769482</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1248903128</t>
+          <t>https://m.place.naver.com/place/1967769482</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4002,34 +3970,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>쏭쏭네일</t>
+          <t>아이샵</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>sun525452@naver.com</t>
+          <t>ishopcare@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>053-611-8445</t>
+          <t>0507-1359-7653</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 현풍중앙로 36 1층</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로 873 1층 아이샵</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sun525452</t>
+          <t>https://open.kakao.com/o/s6hvsDAc</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4039,7 +4007,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4050,7 +4018,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4059,13 +4027,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="R39" t="n">
-        <v>3</v>
+        <v>134</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4074,17 +4042,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>63179444</t>
+          <t>1616404575</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/63179444</t>
+          <t>https://m.place.naver.com/place/1616404575</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4096,29 +4064,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>네일누림 현풍테크노폴리스점</t>
+          <t>쏭쏭네일</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>chelba789@naver.com</t>
+          <t>sun525452@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1489-4282</t>
+          <t>053-611-8445</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노상업로 111 테크노폴리스4단지 상가동 1층 105호</t>
+          <t>대구광역시 달성군 현풍읍 현풍중앙로 36 1층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/sun525452</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4128,12 +4096,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4149,17 +4117,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>107</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>111</v>
+        <v>3</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4168,17 +4136,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1028594389</t>
+          <t>63179444</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1028594389</t>
+          <t>https://m.place.naver.com/place/63179444</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4190,12 +4158,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일하이</t>
+          <t>네일헤몬 대구다사점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>dojulie@naver.com</t>
+          <t>yooywyooyw@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -4203,12 +4171,12 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노북로 33-5 1층</t>
+          <t>대구광역시 달성군 다사읍 대실역북로 55 동화아이위시상가 301동103호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailhigh2021</t>
+          <t>https://www.instagram.com/nailhemon_dasa</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4243,13 +4211,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q41" t="n">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="R41" t="n">
-        <v>3</v>
+        <v>91</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4258,17 +4226,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1919866561</t>
+          <t>1440312692</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1919866561</t>
+          <t>https://m.place.naver.com/place/1440312692</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4280,12 +4248,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>샵손톱에물들다화원</t>
+          <t>루미네일</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>wldms141300@naver.com</t>
+          <t>jine_blog@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -4293,12 +4261,12 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 화원로1길 46-11 1층</t>
+          <t>대구광역시 달성군 옥포읍 돌미상업로2길 26 1층 루미네일</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wldms141300</t>
+          <t>https://www.instagram.com/lume._.nailllll</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4313,7 +4281,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4329,17 +4297,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="Q42" t="n">
-        <v>315</v>
+        <v>29</v>
       </c>
       <c r="R42" t="n">
-        <v>335</v>
+        <v>57</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4348,17 +4316,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1840469863</t>
+          <t>2070020547</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1840469863</t>
+          <t>https://m.place.naver.com/place/2070020547</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4370,20 +4338,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>네일샵</t>
+          <t>슈니네일</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>bitna0614@naver.com</t>
+          <t>flower_lar@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1391-4447</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 화원로 29</t>
+          <t>대구광역시 달성군 현풍읍 현풍로6길 5 청춘난장 301호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4423,14 +4395,14 @@
         </is>
       </c>
       <c r="P43" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2</v>
+      </c>
+      <c r="R43" t="n">
         <v>9</v>
       </c>
-      <c r="Q43" t="n">
-        <v>1</v>
-      </c>
-      <c r="R43" t="n">
-        <v>10</v>
-      </c>
       <c r="S43" t="inlineStr">
         <is>
           <t>X</t>
@@ -4438,17 +4410,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1210929171</t>
+          <t>1526883475</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1210929171</t>
+          <t>https://m.place.naver.com/place/1526883475</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4460,29 +4432,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>네일, The 예쁨</t>
+          <t>류블리뷰티</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>5haveagoodday@naver.com</t>
+          <t>kdskds4329@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>0507-1493-0919</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 매곡로12길 26 1층 106호</t>
+          <t>대구광역시 달성군 다사읍 세천남로 35 제일풍경채 프라임 상가 205동 113호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailtheyebbeum_dasa</t>
+          <t>https://www.instagram.com/youvely_beauty</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4517,13 +4485,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R44" t="n">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4532,17 +4500,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1004489689</t>
+          <t>1137133002</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1004489689</t>
+          <t>https://m.place.naver.com/place/1137133002</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4554,25 +4522,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>모이제이뷰티 현풍테크노폴리스점</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>넬스아이</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>nailseye@naver.com</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1446-0309</t>
+          <t>0507-1447-0487</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노중앙대로 240 한라하우젠트 2층 209호</t>
+          <t>대구광역시 달성군 현풍읍 현풍중앙로10길 73-1 1층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>http://instagram.com/moi.j_beauty</t>
+          <t>https://blog.naver.com/nailseye</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4587,7 +4559,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4607,13 +4579,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>310</v>
+        <v>116</v>
       </c>
       <c r="Q45" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R45" t="n">
-        <v>325</v>
+        <v>133</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4622,17 +4594,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1161931493</t>
+          <t>1482658786</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161931493</t>
+          <t>https://m.place.naver.com/place/1482658786</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4644,29 +4616,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>채채네일</t>
+          <t>제이네일&amp;뷰티</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>aromi486kr@naver.com</t>
+          <t>bomi0306@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1361-6446</t>
+          <t>0507-1435-0221</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노중앙대로6길 16-10 1층 103호 채채네일</t>
+          <t>대구광역시 달성군 다사읍 대실역남로2길 8-6 J:Nail&amp;beauty</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sChJDaCh</t>
+          <t>http://instagram.com/jnail0221</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4692,7 +4664,7 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4701,13 +4673,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>114</v>
+        <v>233</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>114</v>
+        <v>233</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4716,17 +4688,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2031524021</t>
+          <t>1167804147</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2031524021</t>
+          <t>https://m.place.naver.com/place/1167804147</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4738,20 +4710,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>디오르뷰티</t>
+          <t>심쿵뷰티</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>kangvely224@naver.com</t>
+          <t>pselll@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1356-4777</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노북로 260 201동 1124호</t>
+          <t>대구광역시 달성군 유가읍 테크노북로 260 애비뉴스완상가 1103호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4791,13 +4767,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R47" t="n">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4806,17 +4782,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1978929871</t>
+          <t>1422631134</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1978929871</t>
+          <t>https://m.place.naver.com/place/1422631134</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4828,29 +4804,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>석네일 뷰티</t>
+          <t>네일리영</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>heesun0077@naver.com</t>
+          <t>2090063@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1383-4045</t>
+          <t>0507-1375-4992</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 세천본길 45-8 1층 석네일뷰티</t>
+          <t>대구광역시 달성군 현풍읍 테크노상업로 68 센텀타워1층 후면 네일리영</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/naily_yeong</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4860,7 +4836,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4881,17 +4857,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Q48" t="n">
         <v>5</v>
       </c>
       <c r="R48" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4900,17 +4876,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1784441305</t>
+          <t>1456853511</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1784441305</t>
+          <t>https://m.place.naver.com/place/1456853511</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4922,16 +4898,24 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>네일또와</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>샵네일</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>tiger9313@naver.com</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1316-6657</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노상업로 26 108호</t>
+          <t>대구광역시 달성군 현풍읍 비슬로134길 141-6</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4971,13 +4955,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -4986,17 +4970,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2002873448</t>
+          <t>1655717249</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2002873448</t>
+          <t>https://m.place.naver.com/place/1655717249</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5008,34 +4992,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>바르다네일</t>
+          <t>뷰티에디트</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>seolaj@naver.com</t>
+          <t>jyhwang317@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1317-7634</t>
+          <t>0507-1381-3093</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 대실역남로 34 1층 106호</t>
+          <t>대구광역시 달성군 현풍읍 테크노상업로 52 201호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/CgmM1uHLvC_/?igshid=YmMyMTA2M2Y=</t>
+          <t>https://www.instagram.com/nail_by_sj</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5045,7 +5029,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5065,13 +5049,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>10</v>
+        <v>211</v>
       </c>
       <c r="Q50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R50" t="n">
-        <v>16</v>
+        <v>218</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5080,17 +5064,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1585213142</t>
+          <t>1651900268</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1585213142</t>
+          <t>https://m.place.naver.com/place/1651900268</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5102,29 +5086,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>더고은네일 대구화원점</t>
+          <t>임블리제네일</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>thegoeunnail@naver.com</t>
+          <t>j333ok@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1380-6762</t>
+          <t>0507-1329-2089</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 비슬로 2545 화원이진캐스빌상가 110동 2층 220호</t>
+          <t>대구광역시 달성군 옥포읍 돌미로2길 18 임블리제</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thegoeunnail</t>
+          <t>https://www.instagram.com/imblige</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5139,7 +5123,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5150,7 +5134,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5159,13 +5143,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>697</v>
+        <v>72</v>
       </c>
       <c r="Q51" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="R51" t="n">
-        <v>748</v>
+        <v>75</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5174,17 +5158,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1283196595</t>
+          <t>1446451273</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1283196595</t>
+          <t>https://m.place.naver.com/place/1446451273</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5196,25 +5180,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>썸네일 대구다사점</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>W뷰티</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>wbeautykorea@naver.com</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0507-1331-7260</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 대실역북로5길 54-18 1층 101호</t>
+          <t>대구광역시 달성군 다사읍 서재로 140 1층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/so.me_nail</t>
+          <t>http://instagram.com/w_beauty777</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5249,13 +5233,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>194</v>
+        <v>4</v>
       </c>
       <c r="Q52" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>212</v>
+        <v>4</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5264,17 +5248,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1932038368</t>
+          <t>1781318151</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1932038368</t>
+          <t>https://m.place.naver.com/place/1781318151</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5286,29 +5270,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>임블리제네일</t>
+          <t>지니네일</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>j333ok@naver.com</t>
+          <t>goto_seoul@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1329-2089</t>
+          <t>0507-1389-4020</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 옥포읍 돌미로2길 18 임블리제</t>
+          <t>대구광역시 달성군 옥포읍 비슬로447길 11 달성삼환나우빌 301동 102호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/imblige</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5318,7 +5302,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5339,17 +5323,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5358,17 +5342,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1446451273</t>
+          <t>1621609186</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1446451273</t>
+          <t>https://m.place.naver.com/place/1621609186</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5380,25 +5364,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>스페이스 블링</t>
+          <t>솜솜네일</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>mong_s_0810@naver.com</t>
+          <t>mydbfla33@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1384-9259</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노북로 260 2층 2164호(예미지 상가)</t>
+          <t>대구광역시 달성군 유가읍 현풍로47길 67 화이트캐슬 101호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/somsom.nail2</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5408,7 +5396,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5429,17 +5417,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>175</v>
+        <v>11</v>
       </c>
       <c r="Q54" t="n">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="R54" t="n">
-        <v>231</v>
+        <v>30</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5448,17 +5436,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>2080831582</t>
+          <t>1791561455</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2080831582</t>
+          <t>https://m.place.naver.com/place/1791561455</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5470,34 +5458,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>몽디네일 현풍테크노폴리스점</t>
+          <t>미니네일</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>chelba789@naver.com</t>
+          <t>mymomy1202@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1358-9310</t>
+          <t>0507-1427-0344</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노중앙대로6길 16-6 1층 몽디네일</t>
+          <t>대구광역시 달성군 현풍읍 테크노중앙대로 243 1층 118호(타임스퀘어)</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_bXNxkG</t>
+          <t>https://www.instagram.com/mini.nail0101</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5518,7 +5506,7 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5527,13 +5515,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="R55" t="n">
-        <v>162</v>
+        <v>7</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5542,17 +5530,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1572731285</t>
+          <t>1657933953</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1572731285</t>
+          <t>https://m.place.naver.com/place/1657933953</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5564,20 +5552,24 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>최은영네일</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>미자네일</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>misajayeon@naver.com</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1450-8017</t>
+          <t>053-583-7282</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 죽곡2길 3</t>
+          <t>대구광역시 달성군 다사읍 서재로7길 25 동화아이위시3차 상가602동 107호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5617,10 +5609,10 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R56" t="n">
         <v>3</v>
@@ -5632,17 +5624,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1205170846</t>
+          <t>20771150</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1205170846</t>
+          <t>https://m.place.naver.com/place/20771150</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5654,29 +5646,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>넬스아이</t>
+          <t>네일또와</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>nailseye@naver.com</t>
+          <t>sj330035@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>0507-1447-0487</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 현풍중앙로10길 73-1 1층</t>
+          <t>대구광역시 달성군 현풍읍 테크노상업로 26 108호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailseye</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5686,12 +5674,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5707,17 +5695,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5726,17 +5714,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1482658786</t>
+          <t>2002873448</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1482658786</t>
+          <t>https://m.place.naver.com/place/2002873448</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5748,25 +5736,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>더착한네일 2호점</t>
+          <t>네일트렌드제이 다사대실역점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>yujiny43@naver.com</t>
+          <t>happy_y119@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1365-1789</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 세천로 108 앙코르라구나 2층 더착한네일</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로 878 2층 (설빙 옆)</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>http://instagram.com/the_kind_nail2</t>
+          <t>https://linktr.ee/nailtrendj</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5792,22 +5784,22 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>10</v>
+        <v>473</v>
       </c>
       <c r="Q58" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R58" t="n">
-        <v>99</v>
+        <v>565</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5816,17 +5808,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1959040418</t>
+          <t>21607795</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1959040418</t>
+          <t>https://m.place.naver.com/place/21607795</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5838,21 +5830,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>꾸밈네일</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>예쁘다니손</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>rhdwn910@naver.com</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>053-582-4141</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 서재로30길 17 보성1차상가 101호 꾸밈네일</t>
+          <t>대구광역시 달성군 다사읍 세천로 160</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/_y_s2</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5878,22 +5878,22 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="Q59" t="n">
-        <v>61</v>
+        <v>146</v>
       </c>
       <c r="R59" t="n">
-        <v>63</v>
+        <v>170</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5902,17 +5902,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>706872304</t>
+          <t>1241226738</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/706872304</t>
+          <t>https://m.place.naver.com/place/1241226738</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5924,29 +5924,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>모인뷰티</t>
+          <t>네일데이</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>goldminy@naver.com</t>
+          <t>honey126@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1374-7011</t>
+          <t>0507-1385-4658</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 화원로1길 46-8 1층</t>
+          <t>대구광역시 달성군 다사읍 대실역북로4길 6 1층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moin_beauty</t>
+          <t>https://www.instagram.com/https://www.instagram.com/nail_day_k?igsh=eGpma3JucTN6Ymp4</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5981,13 +5981,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -5996,17 +5996,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1855496054</t>
+          <t>1302571156</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1855496054</t>
+          <t>https://m.place.naver.com/place/1302571156</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6018,31 +6018,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>네일은 맑음</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>네일티라노 현풍</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>puri12@naver.com</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1364-3106</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노상업로2길 7-12 2층 204호</t>
+          <t>대구광역시 달성군 유가읍 테크노중앙대로 240 한라하우젠트 상가 1층 120호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_DIXNK/friend</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6058,22 +6066,22 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2</v>
+        <v>140</v>
       </c>
       <c r="Q61" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="R61" t="n">
-        <v>6</v>
+        <v>152</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6082,17 +6090,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1395910390</t>
+          <t>1340647385</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1395910390</t>
+          <t>https://m.place.naver.com/place/1340647385</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6104,25 +6112,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>오늘도네일</t>
+          <t>룩네일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>j2lang@naver.com</t>
+          <t>4chi_27@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1307-5776</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 구지면 과학마을로3길 15 1층</t>
+          <t>대구광역시 달성군 옥포읍 돌미로 50 2층 201호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oneuldo__nail/</t>
+          <t>http://instagram.com/Lo_oknail</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6157,13 +6169,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="Q62" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R62" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6172,17 +6184,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1331774074</t>
+          <t>1257117862</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1331774074</t>
+          <t>https://m.place.naver.com/place/1257117862</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6194,25 +6206,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>네일트렌드제이 다사대실역점</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>샤네일</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>jgy5220@naver.com</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1365-1789</t>
+          <t>0507-1461-4143</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로 878 2층 (설빙 옆)</t>
+          <t>대구광역시 달성군 옥포읍 돌미상업로 10 1층 109호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://linktr.ee/nailtrendj</t>
+          <t>http://instagram.com/chanail_4141</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6238,22 +6254,22 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>473</v>
+        <v>74</v>
       </c>
       <c r="Q63" t="n">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="R63" t="n">
-        <v>565</v>
+        <v>75</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6262,17 +6278,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>21607795</t>
+          <t>1477126656</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21607795</t>
+          <t>https://m.place.naver.com/place/1477126656</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6284,29 +6300,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>딸기네일</t>
+          <t>제이뷰티</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>aquawhta@naver.com</t>
+          <t>ggaau0073@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1403-7930</t>
+          <t>0507-1384-1216</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노중앙대로5길 15-7</t>
+          <t>대구광역시 달성군 구지면 국가산단대로70길 42 상가 1호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/j_beauty_010.4931.1212</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6316,7 +6332,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6337,17 +6353,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6356,17 +6372,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1532741745</t>
+          <t>1507035488</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1532741745</t>
+          <t>https://m.place.naver.com/place/1507035488</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6378,29 +6394,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>뷰티해요</t>
+          <t>딸기네일</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>bonita5332@naver.com</t>
+          <t>aquawhta@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1336-7045</t>
+          <t>0507-1403-7930</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 대실역북로 12 301호</t>
+          <t>대구광역시 달성군 현풍읍 테크노중앙대로5길 15-7</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bonita5332</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6410,12 +6426,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6431,17 +6447,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>91</v>
+        <v>5</v>
       </c>
       <c r="Q65" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>174</v>
+        <v>5</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6450,17 +6466,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1243747619</t>
+          <t>1532741745</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1243747619</t>
+          <t>https://m.place.naver.com/place/1532741745</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6472,21 +6488,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>유닉네일</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>모이제이뷰티 현풍테크노폴리스점</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>wheend@naver.com</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1446-0309</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 현풍중앙로 46-1 1층 유닉네일</t>
+          <t>대구광역시 달성군 유가읍 테크노중앙대로 240 한라하우젠트 2층 209호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/u__nik.nail</t>
+          <t>http://instagram.com/moi.j_beauty</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6521,13 +6545,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>13</v>
+        <v>312</v>
       </c>
       <c r="Q66" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="R66" t="n">
-        <v>15</v>
+        <v>327</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6536,17 +6560,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1621081877</t>
+          <t>1161931493</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1621081877</t>
+          <t>https://m.place.naver.com/place/1161931493</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6558,34 +6582,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>미니네일</t>
+          <t>네일,새벽</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>mymomy1202@naver.com</t>
+          <t>chelba789@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1427-0344</t>
+          <t>0507-1309-4166</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노중앙대로 243 1층 118호(타임스퀘어)</t>
+          <t>대구광역시 달성군 유가읍 테크노북로 260 201동 1층 1121호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mini.nail0101</t>
+          <t>http://pf.kakao.com/_XSGUG</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6606,7 +6630,7 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6615,13 +6639,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="Q67" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R67" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6630,17 +6654,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1657933953</t>
+          <t>1298520181</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1657933953</t>
+          <t>https://m.place.naver.com/place/1298520181</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6652,24 +6676,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>네일을,이쁘게</t>
+          <t>네일스토리</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>gold77com@naver.com</t>
+          <t>yeju0414@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1317-3565</t>
+          <t>053-585-3646</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로 881 1층.107호 네일은,이쁘게</t>
+          <t>대구광역시 달성군 다사읍 서재로7길 25 동화아이위시 3차 상가 2층 601동 203호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6709,13 +6733,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Q68" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R68" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6724,17 +6748,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1456297687</t>
+          <t>36208505</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1456297687</t>
+          <t>https://m.place.naver.com/place/36208505</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6746,25 +6770,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>W뷰티</t>
+          <t>네일플랏</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>wbeautykorea@naver.com</t>
+          <t>jinnny89@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1406-2529</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 서재로 140 1층</t>
+          <t>대구광역시 달성군 옥포읍 돌미상업로 9 화인빌딩 1층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>http://instagram.com/w_beauty777</t>
+          <t>http://instagram.com/nail_plot</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6802,10 +6830,10 @@
         <v>4</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R69" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6814,17 +6842,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1781318151</t>
+          <t>39886025</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1781318151</t>
+          <t>https://m.place.naver.com/place/39886025</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6836,35 +6864,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>네일,새벽</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>석네일 뷰티</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>heesun0077@naver.com</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1309-4166</t>
+          <t>0507-1383-4045</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노북로 260 201동 1층 1121호</t>
+          <t>대구광역시 달성군 다사읍 세천본길 45-8 1층 석네일뷰티</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_XSGUG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6880,22 +6912,22 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R70" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6904,17 +6936,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1298520181</t>
+          <t>1784441305</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1298520181</t>
+          <t>https://m.place.naver.com/place/1784441305</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6926,29 +6958,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>네일하이</t>
+          <t>네일의 온도</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>dojulie@naver.com</t>
+          <t>mistymoon5@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1324-1002</t>
+          <t>0507-1346-1171</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 다사역로 60 다사역 이편한세상 상가 101호</t>
+          <t>대구광역시 달성군 다사읍 세천로 146 1층 102-1호, 네일의온도</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailhi__dasa</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6958,7 +6990,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -6979,17 +7011,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -6998,17 +7030,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>2061866805</t>
+          <t>2090742652</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2061866805</t>
+          <t>https://m.place.naver.com/place/2090742652</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7020,30 +7052,34 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>비네일</t>
+          <t>다비드네일&amp;래쉬 현풍테크노폴리스점</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>eunbi1202@naver.com</t>
+          <t>mipnu3503@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1403-0548</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 서재로 96-1 1층 비네일</t>
+          <t>대구광역시 달성군 유가읍 테크노북로 260 더예미지센트럴 201동 2층 2131호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beenail_bee</t>
+          <t>http://pf.kakao.com/_vlDqG</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7064,7 +7100,7 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7073,13 +7109,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="Q72" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="R72" t="n">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7088,17 +7124,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>36060602</t>
+          <t>1764976820</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36060602</t>
+          <t>https://m.place.naver.com/place/1764976820</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7110,29 +7146,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>미자네일</t>
+          <t>네일을, 이쁘게</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>misajayeon@naver.com</t>
+          <t>loosetime@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>053-583-7282</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 서재로7길 25 동화아이위시3차 상가602동 107호</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로 881 1층 107호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/pretty_nai1_</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7142,7 +7174,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7163,17 +7195,17 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="Q73" t="n">
         <v>2</v>
       </c>
       <c r="R73" t="n">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7182,17 +7214,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>20771150</t>
+          <t>1822297833</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20771150</t>
+          <t>https://m.place.naver.com/place/1822297833</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7204,25 +7236,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>네일살롱</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>진네일</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>jin_nail6453@naver.com</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>053-615-6667</t>
+          <t>0507-1333-6453</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 논공읍 논공로9길 79-6</t>
+          <t>대구광역시 달성군 현풍읍 테크노공원로 17 벨류스퀘어1층113호 진네일</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jin_nail6453</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7232,7 +7268,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7253,17 +7289,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="Q74" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R74" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7272,17 +7308,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1596046698</t>
+          <t>1289979524</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1596046698</t>
+          <t>https://m.place.naver.com/place/1289979524</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7294,12 +7330,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>욜로네일</t>
+          <t>벨라부띠끄</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>s2s20228@naver.com</t>
+          <t>y77777k@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -7307,12 +7343,12 @@
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 옥포읍 돌미로2길 6</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로 874 벨라부띠끄</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>http://instagram.com/yolonail9010</t>
+          <t>http://instagram.com/bellaboutique.nail</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7347,13 +7383,13 @@
         </is>
       </c>
       <c r="P75" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q75" t="n">
         <v>5</v>
       </c>
-      <c r="Q75" t="n">
-        <v>1</v>
-      </c>
       <c r="R75" t="n">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7362,17 +7398,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1935910413</t>
+          <t>1192828282</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1935910413</t>
+          <t>https://m.place.naver.com/place/1192828282</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7384,29 +7420,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>반짝반짝네일</t>
+          <t>부베니르 네일</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>dkw05026@naver.com</t>
+          <t>bliss_322@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>053-581-0210</t>
+          <t>0507-1414-4481</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 서재로27길 42 신성서화성파크드림상가 301동 102호</t>
+          <t>대구광역시 달성군 화원읍 화암로 69 명곡시장 안 할매국밥 옆쪽</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/vous_benir_nail/</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7416,7 +7452,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7437,17 +7473,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>14</v>
+        <v>525</v>
       </c>
       <c r="Q76" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="R76" t="n">
-        <v>16</v>
+        <v>571</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7456,17 +7492,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1571722665</t>
+          <t>1474593561</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1571722665</t>
+          <t>https://m.place.naver.com/place/1474593561</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7478,29 +7514,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>뷰티에디트</t>
+          <t>엄지공주뷰티샵</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>jyhwang317@naver.com</t>
+          <t>tosemdnlcl@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1381-3093</t>
+          <t>0507-1358-0830</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노상업로 52 201호</t>
+          <t>대구광역시 달성군 화원읍 명곡로 9 명곡미래빌1단지 상가 2층</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_by_sj</t>
+          <t>https://blog.naver.com/tosemdnlcl</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7515,7 +7551,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -7535,13 +7571,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>209</v>
+        <v>90</v>
       </c>
       <c r="Q77" t="n">
         <v>7</v>
       </c>
       <c r="R77" t="n">
-        <v>216</v>
+        <v>97</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7550,17 +7586,17 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1651900268</t>
+          <t>20061778</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1651900268</t>
+          <t>https://m.place.naver.com/place/20061778</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7572,39 +7608,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>코지무이</t>
+          <t>최은영네일</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>banglang93@naver.com</t>
+          <t>geochanggun@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0507-1301-4534</t>
+          <t>0507-1450-8017</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 대실역남로2길 8-5 1층</t>
+          <t>대구광역시 달성군 다사읍 죽곡2길 3</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pGxhus</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7620,7 +7656,7 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7629,13 +7665,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R78" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7644,17 +7680,17 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1306738999</t>
+          <t>1205170846</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1306738999</t>
+          <t>https://m.place.naver.com/place/1205170846</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7666,29 +7702,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>제이네일&amp;뷰티</t>
+          <t>네일반하다</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>bomi0306@naver.com</t>
+          <t>iiijuheeiii@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0507-1435-0221</t>
+          <t>0507-1320-7016</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 대실역남로2길 8-6 J:Nail&amp;beauty</t>
+          <t>대구광역시 달성군 유가읍 테크노순환로 423 중흥S클래스 아파트 상가 2층 203호</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>http://instagram.com/jnail0221</t>
+          <t>https://www.instagram.com/yoomi_nail_banhada</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7723,13 +7759,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R79" t="n">
-        <v>233</v>
+        <v>1</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7738,17 +7774,17 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1167804147</t>
+          <t>1903028426</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1167804147</t>
+          <t>https://m.place.naver.com/place/1903028426</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7760,34 +7796,34 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>다비드네일&amp;래쉬 현풍테크노폴리스점</t>
+          <t>뷰티플랏</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>mipnu3503@naver.com</t>
+          <t>123ggo@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0507-1403-0548</t>
+          <t>0507-1333-4551</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노북로 260 더예미지센트럴 201동 2층 2131호</t>
+          <t>대구광역시 달성군 구지면 과학마을로 51-1 뷰티플랏</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_vlDqG</t>
+          <t>http://instagram.com/beauty_plot</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7808,7 +7844,7 @@
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -7817,13 +7853,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="Q80" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="R80" t="n">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7832,17 +7868,17 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>1764976820</t>
+          <t>1623449679</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1764976820</t>
+          <t>https://m.place.naver.com/place/1623449679</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7854,34 +7890,34 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>수이네일 다사대실역점</t>
+          <t>바르다네일</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>sweets0101@naver.com</t>
+          <t>seolaj@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0507-1423-4145</t>
+          <t>0507-1317-7634</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로174길 50 죽곡협성휴포레 상가 301동 105호</t>
+          <t>대구광역시 달성군 다사읍 대실역남로 34 1층 106호</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sui.nail.shop</t>
+          <t>https://www.instagram.com/p/CgmM1uHLvC_/?igshid=YmMyMTA2M2Y=</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -7891,7 +7927,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -7911,13 +7947,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="Q81" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R81" t="n">
-        <v>107</v>
+        <v>16</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -7926,17 +7962,17 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1939839368</t>
+          <t>1585213142</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1939839368</t>
+          <t>https://m.place.naver.com/place/1585213142</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7948,29 +7984,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>슈니네일</t>
+          <t>네일,또만나</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>swim_ming_@naver.com</t>
+          <t>deepgriep29@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0507-1391-4447</t>
+          <t>0507-1356-9059</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 현풍로6길 5 청춘난장 301호</t>
+          <t>대구광역시 달성군 구지면 국가산단북로60길 66 1층 103호</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_ttomanna</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7980,7 +8016,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -8001,17 +8037,17 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Q82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8020,17 +8056,17 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1526883475</t>
+          <t>2071071912</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1526883475</t>
+          <t>https://m.place.naver.com/place/2071071912</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8042,30 +8078,34 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>류블리뷰티</t>
+          <t>코지무이</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>kdskds4329@naver.com</t>
+          <t>banglang93@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1301-4534</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 세천남로 35 제일풍경채 프라임 상가 205동 113호</t>
+          <t>대구광역시 달성군 다사읍 대실역남로2길 8-5 1층</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/youvely_beauty</t>
+          <t>http://pf.kakao.com/_pGxhus</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8086,22 +8126,22 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>119</v>
+        <v>4</v>
       </c>
       <c r="Q83" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="R83" t="n">
-        <v>135</v>
+        <v>11</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8110,17 +8150,17 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1137133002</t>
+          <t>1306738999</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1137133002</t>
+          <t>https://m.place.naver.com/place/1306738999</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8132,21 +8172,25 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>공감네일</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
+          <t>더착한네일 2호점</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>yujiny43@naver.com</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노공원로 73 2층 공감네일</t>
+          <t>대구광역시 달성군 다사읍 세천로 108 앙코르라구나 2층 더착한네일</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/the_kind_nail2</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8156,7 +8200,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -8177,17 +8221,17 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q84" t="n">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="R84" t="n">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8196,17 +8240,17 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1835125814</t>
+          <t>1959040418</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835125814</t>
+          <t>https://m.place.naver.com/place/1959040418</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8218,25 +8262,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>정민뷰티</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
+          <t>네일살롱</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>wing3527@naver.com</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0507-1325-7846</t>
+          <t>053-615-6667</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 구지면 과학마을로2길 71 1층</t>
+          <t>대구광역시 달성군 논공읍 논공로9길 79-6</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://cafe.naver.com/jastyle</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8246,12 +8294,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8267,17 +8315,17 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R85" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8286,17 +8334,17 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1739070946</t>
+          <t>1596046698</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1739070946</t>
+          <t>https://m.place.naver.com/place/1596046698</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8308,39 +8356,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>네일안</t>
+          <t>제이오뷰티 다사대실역점</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>sjnr27@naver.com</t>
+          <t>happy_y119@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0507-1419-1224</t>
+          <t>0507-1372-0952</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노중앙대로5길 15-3 1층 네일안</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로 846-1 제이오뷰티</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/sc9akTld</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -8356,22 +8404,22 @@
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P86" t="n">
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8380,17 +8428,17 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1568448625</t>
+          <t>1940949870</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1568448625</t>
+          <t>https://m.place.naver.com/place/1940949870</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8402,34 +8450,34 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>레비라네일 현풍테크노폴리스점</t>
+          <t>오늘네일 다사대실점</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>apple6931@naver.com</t>
+          <t>yuri3935@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1430-5033</t>
+          <t>0507-1480-2662</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노북로 260 예미지상가 2171호</t>
+          <t>대구광역시 달성군 다사읍 대실역북로 70 1층 오늘네일</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_YJxhxlG</t>
+          <t>https://www.instagram.com/oneul_nail80</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -8450,7 +8498,7 @@
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -8459,13 +8507,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="Q87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R87" t="n">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8474,17 +8522,17 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1808169841</t>
+          <t>1867576541</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1808169841</t>
+          <t>https://m.place.naver.com/place/1867576541</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8496,29 +8544,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Nail,On</t>
+          <t>공감네일</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>cara1982@naver.com</t>
+          <t>finger1229@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>0507-1446-3385</t>
-        </is>
-      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 구지면 과학마을로5길 45 1층</t>
+          <t>대구광역시 달성군 유가읍 테크노공원로 73 2층 공감네일</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.on__</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8528,7 +8572,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -8549,17 +8593,17 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="Q88" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R88" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8568,17 +8612,17 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>2080619879</t>
+          <t>1835125814</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2080619879</t>
+          <t>https://m.place.naver.com/place/1835125814</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8634,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>뷰티박스</t>
+          <t>샵손톱에물들다화원</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>dasom4343@naver.com</t>
+          <t>wldms141300@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -8603,12 +8647,12 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 세천로 182-10 현대 썬앤빌상가 302동 104호</t>
+          <t>대구광역시 달성군 화원읍 화원로1길 46-11 1층</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beauty__box_j</t>
+          <t>https://blog.naver.com/wldms141300</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8623,7 +8667,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -8639,17 +8683,17 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Q89" t="n">
-        <v>8</v>
+        <v>315</v>
       </c>
       <c r="R89" t="n">
-        <v>10</v>
+        <v>335</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8658,17 +8702,17 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1149958107</t>
+          <t>1840469863</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1149958107</t>
+          <t>https://m.place.naver.com/place/1840469863</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8680,25 +8724,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>네일플랏</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
+          <t>남자다운네일</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>kfood011@naver.com</t>
+        </is>
+      </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0507-1406-2529</t>
+          <t>053-582-7676</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 옥포읍 돌미상업로 9 화인빌딩 1층</t>
+          <t>대구광역시 달성군 다사읍 세천북로 13</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_plot</t>
+          <t>https://blog.naver.com/kfood011</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8713,7 +8761,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -8729,17 +8777,17 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q90" t="n">
         <v>16</v>
       </c>
       <c r="R90" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8748,17 +8796,17 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>39886025</t>
+          <t>218033600</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/39886025</t>
+          <t>https://m.place.naver.com/place/218033600</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8770,29 +8818,25 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>네일써니</t>
+          <t>뷰티박스</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ha780106@naver.com</t>
+          <t>dasom4343@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>0507-1410-7991</t>
-        </is>
-      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 비슬로 2545 상가 110동 3층 310호</t>
+          <t>대구광역시 달성군 다사읍 세천로 182-10 현대 썬앤빌상가 302동 104호</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.sunny7985</t>
+          <t>https://www.instagram.com/beauty__box_j</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8827,13 +8871,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q91" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R91" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8842,17 +8886,17 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1704201083</t>
+          <t>1149958107</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1704201083</t>
+          <t>https://m.place.naver.com/place/1149958107</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8864,29 +8908,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>샤네일</t>
+          <t>모브네일</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>akkion@naver.com</t>
+          <t>jaera423@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0507-1461-4143</t>
+          <t>0507-1327-7428</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 옥포읍 돌미상업로 10 1층 109호</t>
+          <t>대구광역시 달성군 구지면 국가산단대로70길 17 대구국가산단디에트르더센트럴 상가 111호</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>http://instagram.com/chanail_4141</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8896,7 +8940,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -8917,17 +8961,17 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="Q92" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R92" t="n">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -8936,17 +8980,17 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1477126656</t>
+          <t>1135244635</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1477126656</t>
+          <t>https://m.place.naver.com/place/1135244635</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8958,34 +9002,34 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>뮤아드네일</t>
+          <t>채채네일</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>twolee10_@naver.com</t>
+          <t>aromi486kr@naver.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>0507-1312-2226</t>
+          <t>0507-1361-6446</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노중앙대로5길 15-9 1층 101호</t>
+          <t>대구광역시 달성군 유가읍 테크노중앙대로6길 16-10 1층 103호 채채네일</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muad.nail</t>
+          <t>https://open.kakao.com/o/sChJDaCh</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -9006,7 +9050,7 @@
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -9015,13 +9059,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>4</v>
+        <v>115</v>
       </c>
       <c r="Q93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>5</v>
+        <v>115</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -9030,17 +9074,17 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>2002612318</t>
+          <t>2031524021</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2002612318</t>
+          <t>https://m.place.naver.com/place/2031524021</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9052,29 +9096,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>남자다운네일</t>
+          <t>네일안</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>kfood011@naver.com</t>
+          <t>sjnr27@naver.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>053-582-7676</t>
+          <t>0507-1419-1224</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 세천북로 13</t>
+          <t>대구광역시 달성군 현풍읍 테크노중앙대로5길 15-3 1층 네일안</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kfood011</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9084,12 +9128,12 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9109,13 +9153,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9124,17 +9168,17 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>218033600</t>
+          <t>1568448625</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/218033600</t>
+          <t>https://m.place.naver.com/place/1568448625</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9146,29 +9190,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>아이샵</t>
+          <t>맘스네일 현풍점</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ishopcare@naver.com</t>
+          <t>j_hee_2@naver.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0507-1359-7653</t>
+          <t>0507-1334-7625</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로 873 1층 아이샵</t>
+          <t>대구광역시 달성군 유가읍 테크노중앙대로 326-27 1층</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s6hvsDAc</t>
+          <t>https://www.instagram.com/hyunpung_momsnail</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9194,7 +9238,7 @@
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -9203,13 +9247,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>60</v>
+        <v>231</v>
       </c>
       <c r="Q95" t="n">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="R95" t="n">
-        <v>134</v>
+        <v>289</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -9218,17 +9262,17 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>1616404575</t>
+          <t>1058493414</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1616404575</t>
+          <t>https://m.place.naver.com/place/1058493414</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9240,34 +9284,34 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>네일반하다</t>
+          <t>몽디네일 현풍테크노폴리스점</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>iiijuheeiii@naver.com</t>
+          <t>chelba789@naver.com</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0507-1320-7016</t>
+          <t>0507-1358-9310</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노순환로 423 중흥S클래스 아파트 상가 2층 203호</t>
+          <t>대구광역시 달성군 유가읍 테크노중앙대로6길 16-6 1층 몽디네일</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yoomi_nail_banhada</t>
+          <t>http://pf.kakao.com/_bXNxkG</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -9288,7 +9332,7 @@
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -9297,13 +9341,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="Q96" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R96" t="n">
-        <v>1</v>
+        <v>163</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -9312,17 +9356,17 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>1903028426</t>
+          <t>1572731285</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1903028426</t>
+          <t>https://m.place.naver.com/place/1572731285</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9334,24 +9378,20 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>블리스네일</t>
+          <t>디오르뷰티</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>irislove27@naver.com</t>
+          <t>kangvely224@naver.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>0507-1358-3759</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 옥포읍 돌미로 70 대성베르힐 4단지 동문상가 3층 303호</t>
+          <t>대구광역시 달성군 유가읍 테크노북로 260 201동 1124호</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9391,13 +9431,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="Q97" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -9406,17 +9446,17 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>1427642953</t>
+          <t>1978929871</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1427642953</t>
+          <t>https://m.place.naver.com/place/1978929871</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9485,13 +9525,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Q98" t="n">
         <v>1</v>
       </c>
       <c r="R98" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -9510,7 +9550,7 @@
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9522,25 +9562,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>꼼네일</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
+          <t>네일하이</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>dojulie@naver.com</t>
+        </is>
+      </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0507-1334-1563</t>
+          <t>0507-1324-1002</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로174길 50 303호</t>
+          <t>대구광역시 달성군 다사읍 다사역로 60 다사역 이편한세상 상가 101호</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kkom_nail21</t>
+          <t>https://www.instagram.com/nailhi__dasa</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -9575,13 +9619,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Q99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R99" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -9590,17 +9634,17 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>1113405538</t>
+          <t>2061866805</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1113405538</t>
+          <t>https://m.place.naver.com/place/2061866805</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9612,20 +9656,20 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>샵네일</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr"/>
+          <t>네일 예쁘다</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>yooky617@naver.com</t>
+        </is>
+      </c>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>0507-1316-6657</t>
-        </is>
-      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 비슬로134길 141-6</t>
+          <t>대구광역시 달성군 유가읍 테크노상업로 108 2층 205호 네일예쁘다</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -9665,13 +9709,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -9680,17 +9724,17 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>1655717249</t>
+          <t>1252953982</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1655717249</t>
+          <t>https://m.place.naver.com/place/1252953982</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9828,7 @@
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9796,29 +9840,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>예쁘다니손</t>
+          <t>꼼네일</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>rhdwn910@naver.com</t>
+          <t>immire@naver.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>053-582-4141</t>
+          <t>0507-1334-1563</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 세천로 160</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로174길 50 303호</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/_y_s2</t>
+          <t>https://www.instagram.com/kkom_nail21</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9844,7 +9888,7 @@
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -9853,13 +9897,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="Q102" t="n">
-        <v>146</v>
+        <v>1</v>
       </c>
       <c r="R102" t="n">
-        <v>170</v>
+        <v>10</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -9868,52 +9912,56 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>1241226738</t>
+          <t>1113405538</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1241226738</t>
+          <t>https://m.place.naver.com/place/1113405538</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>속눈썹증모,연장</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>아이쁨</t>
+          <t>정민뷰티</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>tjsdnalrud81@naver.com</t>
+          <t>ckchungkang@naver.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0507-1325-7846</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노상업로2길 19 미소빌딩 108호</t>
+          <t>대구광역시 달성군 구지면 과학마을로2길 71 1층</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/eye.bbm</t>
+          <t>https://cafe.naver.com/jastyle</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -9943,32 +9991,122 @@
         </is>
       </c>
       <c r="P103" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>4</v>
+      </c>
+      <c r="R103" t="n">
+        <v>19</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>1739070946</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1739070946</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>속눈썹증모,연장</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>아이쁨</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>tjsdnalrud81@naver.com</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>대구광역시 달성군 현풍읍 테크노상업로2길 19 미소빌딩 108호</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/eye.bbm</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
         <v>8</v>
       </c>
-      <c r="Q103" t="n">
+      <c r="Q104" t="n">
         <v>635</v>
       </c>
-      <c r="R103" t="n">
+      <c r="R104" t="n">
         <v>643</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T103" t="inlineStr">
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
         <is>
           <t>1023950134</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="U104" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1023950134</t>
         </is>
       </c>
-      <c r="V103" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/달성군_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/달성군_네일샵.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,25 +564,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>홀드풋케어 발톱무좀 내성발톱 문제성발관리</t>
+          <t>꼼네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>070-4866-1122</t>
+          <t>0507-1334-1563</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노북로 260 201동 2200호</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로174길 50 303호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/kkom_nail21</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -613,17 +613,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -632,17 +632,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1280044307</t>
+          <t>1113405538</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1280044307</t>
+          <t>https://m.place.naver.com/place/1113405538</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -654,25 +654,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>모인뷰티</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>네일&amp;스킨</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>feel3051@naver.com</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1374-7011</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 화원로1길 46-8 1층</t>
+          <t>대구광역시 달성군 화원읍 화원로7길 54</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moin_beauty</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -703,17 +703,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -722,17 +722,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1855496054</t>
+          <t>38401077</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1855496054</t>
+          <t>https://m.place.naver.com/place/38401077</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -744,35 +744,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>네일은 맑음</t>
+          <t>아이샵</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kkje38317@naver.com</t>
+          <t>ishopcare@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0507-1359-7653</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노상업로2길 7-12 2층 204호</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로 873 1층 아이샵</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/s6hvsDAc</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -788,22 +792,22 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="R4" t="n">
-        <v>6</v>
+        <v>134</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -812,17 +816,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1395910390</t>
+          <t>1616404575</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1395910390</t>
+          <t>https://m.place.naver.com/place/1616404575</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -834,39 +838,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일누림 현풍테크노폴리스점</t>
+          <t>정민뷰티</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>chelba789@naver.com</t>
+          <t>ckchungkang@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1489-4282</t>
+          <t>0507-1325-7846</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노상업로 111 테크노폴리스4단지 상가동 1층 105호</t>
+          <t>대구광역시 달성군 구지면 과학마을로2길 71 1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://cafe.naver.com/jastyle</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -887,17 +891,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>107</v>
+        <v>15</v>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -906,17 +910,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1028594389</t>
+          <t>1739070946</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1028594389</t>
+          <t>https://m.place.naver.com/place/1739070946</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -928,40 +932,44 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>비네일</t>
+          <t>엄지공주뷰티샵</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>eunbi1202@naver.com</t>
+          <t>tosemdnlcl@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1358-0830</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 서재로 96-1 1층 비네일</t>
+          <t>대구광역시 달성군 화원읍 명곡로 9 명곡미래빌1단지 상가 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/jYywkSBMS</t>
+          <t>https://blog.naver.com/tosemdnlcl</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -981,13 +989,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="Q6" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="R6" t="n">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -996,17 +1004,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>36060602</t>
+          <t>20061778</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36060602</t>
+          <t>https://m.place.naver.com/place/20061778</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1018,29 +1026,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>반짝반짝네일</t>
+          <t>네일을, 이쁘게</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dkw05026@naver.com</t>
+          <t>gold77com@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>053-581-0210</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 서재본길 10 1층 101호</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로 881 1층 107호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/pretty_nai1_</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1050,7 +1054,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1071,17 +1075,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>14</v>
+        <v>160</v>
       </c>
       <c r="Q7" t="n">
         <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>16</v>
+        <v>162</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1090,17 +1094,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1571722665</t>
+          <t>1822297833</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1571722665</t>
+          <t>https://m.place.naver.com/place/1822297833</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1112,34 +1116,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일 봄</t>
+          <t>비네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>joolijooli@naver.com</t>
+          <t>eunbi1202@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1306-6012</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로 875 MA프라자 105호</t>
+          <t>대구광역시 달성군 다사읍 서재로 96-1 1층 비네일</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://toss.place/_lb/jYywkSBMS</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="R8" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1419253509</t>
+          <t>36060602</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1419253509</t>
+          <t>https://m.place.naver.com/place/36060602</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1206,16 +1206,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>현네일앤뷰티</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>네일의 온도</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mistymoon5@naver.com</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1346-1171</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 인흥길 83 1층</t>
+          <t>대구광역시 달성군 다사읍 세천로 146 1층 102-1호, 네일의온도</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1255,13 +1263,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1270,17 +1278,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1094979616</t>
+          <t>2090742652</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1094979616</t>
+          <t>https://m.place.naver.com/place/2090742652</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1300,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>미유네일</t>
+          <t>네일채움</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>atsing427@naver.com</t>
+          <t>rhdwnsla5656@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1305,12 +1313,12 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노상업로 34 1층 리차드헤어샵 안</t>
+          <t>대구광역시 달성군 다사읍 대실역북로 66-1 네일채움</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/miyou_nail2023</t>
+          <t>http://instagram.com/jj_ chaewoom</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1345,13 +1353,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1360,17 +1368,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1953875264</t>
+          <t>1840386729</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1953875264</t>
+          <t>https://m.place.naver.com/place/1840386729</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1382,25 +1390,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>호네일</t>
+          <t>모브네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hhhong88@naver.com</t>
+          <t>jaera423@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1327-7428</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 서재로12길 38 에코폴리스 동화아이위시 1차상가 호네일</t>
+          <t>대구광역시 달성군 구지면 국가산단대로70길 17 대구국가산단디에트르더센트럴 상가 111호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ho_nail0999</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1410,7 +1422,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1426,22 +1438,22 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1450,17 +1462,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1248903128</t>
+          <t>1135244635</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1248903128</t>
+          <t>https://m.place.naver.com/place/1135244635</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1472,29 +1484,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>수이네일 다사대실역점</t>
+          <t>지니네일</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sweets0101@naver.com</t>
+          <t>goto_seoul@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1423-4145</t>
+          <t>0507-1389-4020</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로174길 50 죽곡협성휴포레 상가 301동 105호</t>
+          <t>대구광역시 달성군 옥포읍 비슬로447길 11 달성삼환나우빌 301동 102호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sui.nail.shop</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1504,7 +1516,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1525,17 +1537,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1544,17 +1556,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1939839368</t>
+          <t>1621609186</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1939839368</t>
+          <t>https://m.place.naver.com/place/1621609186</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1566,34 +1578,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>레비라네일 현풍테크노폴리스점</t>
+          <t>남자다운네일</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>apple6931@naver.com</t>
+          <t>kfood011@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1430-5033</t>
+          <t>053-582-7676</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노북로 260 예미지상가 2171호</t>
+          <t>대구광역시 달성군 다사읍 세천북로 13</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_YJxhxlG</t>
+          <t>https://blog.naver.com/kfood011</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1603,7 +1615,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1614,22 +1626,22 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>155</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="R13" t="n">
-        <v>159</v>
+        <v>19</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1638,17 +1650,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1808169841</t>
+          <t>218033600</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1808169841</t>
+          <t>https://m.place.naver.com/place/218033600</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1660,25 +1672,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>유닉네일</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>bdt9947@naver.com</t>
-        </is>
-      </c>
+          <t>뷰티에디트</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1381-3093</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 현풍중앙로 46-1 1층 유닉네일</t>
+          <t>대구광역시 달성군 현풍읍 테크노상업로 52 201호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/u__nik.nail</t>
+          <t>https://www.instagram.com/nail_by_sj</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1713,13 +1725,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>13</v>
+        <v>211</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R14" t="n">
-        <v>15</v>
+        <v>219</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1728,17 +1740,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1621081877</t>
+          <t>1651900268</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1621081877</t>
+          <t>https://m.place.naver.com/place/1651900268</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1750,25 +1762,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>오늘도네일</t>
+          <t>임블리제네일</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>j2lang@naver.com</t>
+          <t>j333ok@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1329-2089</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 구지면 과학마을로3길 15 1층</t>
+          <t>대구광역시 달성군 옥포읍 돌미로2길 18 임블리제</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oneuldo__nail/</t>
+          <t>https://www.instagram.com/imblige</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1803,13 +1819,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1818,17 +1834,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1331774074</t>
+          <t>1446451273</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1331774074</t>
+          <t>https://m.place.naver.com/place/1446451273</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1840,20 +1856,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>네일샵</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>bitna0614@naver.com</t>
-        </is>
-      </c>
+          <t>네일은 맑음</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 화원로 29</t>
+          <t>대구광역시 달성군 현풍읍 테크노상업로2길 7-12 2층 204호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1893,13 +1905,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1908,17 +1920,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1210929171</t>
+          <t>1395910390</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1210929171</t>
+          <t>https://m.place.naver.com/place/1395910390</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1930,29 +1942,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>예쁘제네일뷰티</t>
+          <t>W뷰티</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>shimaroma@naver.com</t>
+          <t>wbeautykorea@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1330-4637</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 구지면 과학마을로2길 6 상가1층 예쁘제</t>
+          <t>대구광역시 달성군 다사읍 서재로 140 1층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_yeppeuje</t>
+          <t>http://instagram.com/w_beauty777</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1987,13 +1995,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2002,17 +2010,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1482366649</t>
+          <t>1781318151</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1482366649</t>
+          <t>https://m.place.naver.com/place/1781318151</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2024,25 +2032,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>꾸밈네일</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>smileahj@naver.com</t>
-        </is>
-      </c>
+          <t>제이네일&amp;뷰티</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1435-0221</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 서재로30길 17 보성1차상가 101호 꾸밈네일</t>
+          <t>대구광역시 달성군 다사읍 대실역남로2길 8-6 J:Nail&amp;beauty</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/jnail0221</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2052,7 +2060,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2073,17 +2081,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>233</v>
       </c>
       <c r="Q18" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>63</v>
+        <v>233</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2092,17 +2100,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>706872304</t>
+          <t>1167804147</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/706872304</t>
+          <t>https://m.place.naver.com/place/1167804147</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2114,29 +2122,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>네일써니</t>
+          <t>예쁘제네일뷰티</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ha780106@naver.com</t>
+          <t>shimaroma@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1410-7991</t>
+          <t>0507-1330-4637</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 비슬로 2545 상가 110동 3층 310호</t>
+          <t>대구광역시 달성군 구지면 과학마을로2길 6 상가1층 예쁘제</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.sunny7985</t>
+          <t>http://instagram.com/nail_yeppeuje</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2174,10 +2182,10 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2186,17 +2194,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1704201083</t>
+          <t>1482366649</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1704201083</t>
+          <t>https://m.place.naver.com/place/1482366649</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2208,29 +2216,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>썸네일 대구다사점</t>
+          <t>쏭쏭네일</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>yooywyooyw@naver.com</t>
+          <t>sun525452@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1331-7260</t>
+          <t>053-611-8445</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 대실역북로5길 54-18 1층 101호</t>
+          <t>대구광역시 달성군 현풍읍 현풍중앙로 36 1층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/so.me_nail</t>
+          <t>https://blog.naver.com/sun525452</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2245,7 +2253,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2265,13 +2273,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>195</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>213</v>
+        <v>3</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2280,17 +2288,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1932038368</t>
+          <t>63179444</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1932038368</t>
+          <t>https://m.place.naver.com/place/63179444</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2302,29 +2310,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>네일을,이쁘게</t>
+          <t>룩네일</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>loosetime@naver.com</t>
+          <t>4chi_27@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1317-3565</t>
+          <t>0507-1307-5776</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로 881 1층.107호 네일은,이쁘게</t>
+          <t>대구광역시 달성군 옥포읍 돌미로 50 2층 201호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/Lo_oknail</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2334,7 +2342,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2355,17 +2363,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="Q21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2374,17 +2382,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1456297687</t>
+          <t>1257117862</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1456297687</t>
+          <t>https://m.place.naver.com/place/1257117862</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2396,29 +2404,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>뮤아드네일</t>
+          <t>유닉네일</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>twolee10_@naver.com</t>
+          <t>bdt9947@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0507-1312-2226</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노중앙대로5길 15-9 1층 101호</t>
+          <t>대구광역시 달성군 현풍읍 현풍중앙로 46-1 1층 유닉네일</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muad.nail</t>
+          <t>https://www.instagram.com/u__nik.nail</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2453,13 +2457,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2468,17 +2472,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2002612318</t>
+          <t>1621081877</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2002612318</t>
+          <t>https://m.place.naver.com/place/1621081877</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2490,25 +2494,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>네일&amp;스킨</t>
+          <t>맘스네일 현풍점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>feel3051@naver.com</t>
+          <t>j_hee_2@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1334-7625</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 화원로7길 54</t>
+          <t>대구광역시 달성군 유가읍 테크노중앙대로 326-27 1층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/hyunpung_momsnail</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2518,7 +2526,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2539,17 +2547,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>231</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>289</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2558,17 +2566,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>38401077</t>
+          <t>1058493414</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38401077</t>
+          <t>https://m.place.naver.com/place/1058493414</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2580,29 +2588,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>으니네일</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>gost5544@naver.com</t>
-        </is>
-      </c>
+          <t>샤네일</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1385-1093</t>
+          <t>0507-1461-4143</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로174길 21 2층</t>
+          <t>대구광역시 달성군 옥포읍 돌미상업로 10 1층 109호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/euni__nail</t>
+          <t>http://instagram.com/chanail_4141</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2637,13 +2641,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2652,17 +2656,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1662155594</t>
+          <t>1477126656</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1662155594</t>
+          <t>https://m.place.naver.com/place/1477126656</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2674,25 +2678,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>욜로네일</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>s2s20228@naver.com</t>
-        </is>
-      </c>
+          <t>네일리영</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1375-4992</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 옥포읍 돌미로2길 6</t>
+          <t>대구광역시 달성군 현풍읍 테크노상업로 68 센텀타워1층 후면 네일리영</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>http://instagram.com/yolonail9010</t>
+          <t>https://www.instagram.com/naily_yeong</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2727,13 +2731,13 @@
         </is>
       </c>
       <c r="P25" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q25" t="n">
         <v>5</v>
       </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
       <c r="R25" t="n">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2742,17 +2746,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1935910413</t>
+          <t>1456853511</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1935910413</t>
+          <t>https://m.place.naver.com/place/1456853511</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2764,29 +2768,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>네일하담</t>
+          <t>썸네일 대구다사점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mementomori-24@naver.com</t>
+          <t>yooywyooyw@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1318-5676</t>
+          <t>0507-1331-7260</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 논공읍 논공로9길 68 2층</t>
+          <t>대구광역시 달성군 다사읍 대실역북로5길 54-18 1층 101호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailhadam_</t>
+          <t>https://www.instagram.com/so.me_nail</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2821,13 +2825,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>214</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2836,17 +2840,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1157430781</t>
+          <t>1932038368</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1157430781</t>
+          <t>https://m.place.naver.com/place/1932038368</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2858,29 +2862,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>뷰티해요</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>bonita5332@naver.com</t>
-        </is>
-      </c>
+          <t>혜진뷰티</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1336-7045</t>
+          <t>0507-1306-5661</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 대실역북로 12 301호</t>
+          <t>대구광역시 달성군 화원읍 화원로2길 13 1층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bonita5332</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2890,12 +2890,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2911,17 +2911,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="Q27" t="n">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="R27" t="n">
-        <v>176</v>
+        <v>100</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2930,17 +2930,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1243747619</t>
+          <t>1025452354</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1243747619</t>
+          <t>https://m.place.naver.com/place/1025452354</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2952,29 +2952,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>블리스네일</t>
+          <t>진네일</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>lee0ja8850@naver.com</t>
+          <t>jin_nail6453@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1358-3759</t>
+          <t>0507-1333-6453</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 옥포읍 돌미로 70 대성베르힐 4단지 동문상가 3층 303호</t>
+          <t>대구광역시 달성군 현풍읍 테크노공원로 17 벨류스퀘어1층113호 진네일</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jin_nail6453</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3005,17 +3005,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="Q28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R28" t="n">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3024,17 +3024,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1427642953</t>
+          <t>1289979524</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1427642953</t>
+          <t>https://m.place.naver.com/place/1289979524</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3046,25 +3046,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>네일채움</t>
+          <t>네일트렌드제이 다사대실역점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>rhdwnsla5656@naver.com</t>
+          <t>happy_y119@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1365-1789</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 대실역북로 66-1 네일채움</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로 878 2층 (설빙 옆)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>http://instagram.com/jj_ chaewoom</t>
+          <t>https://linktr.ee/nailtrendj</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3090,22 +3094,22 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>5</v>
+        <v>473</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>92</v>
       </c>
       <c r="R29" t="n">
-        <v>9</v>
+        <v>565</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3114,17 +3118,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1840386729</t>
+          <t>21607795</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1840386729</t>
+          <t>https://m.place.naver.com/place/21607795</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3136,35 +3140,35 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>스페이스 블링</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>mong_s_0810@naver.com</t>
-        </is>
-      </c>
+          <t>제이오뷰티 다사대실역점</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1372-0952</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노북로 260 2층 2164호(예미지 상가)</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로 846-1 제이오뷰티</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/sc9akTld</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3180,22 +3184,22 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="R30" t="n">
-        <v>232</v>
+        <v>42</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3204,17 +3208,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2080831582</t>
+          <t>1940949870</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2080831582</t>
+          <t>https://m.place.naver.com/place/1940949870</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3226,29 +3230,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>혜진뷰티</t>
+          <t>미유네일</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jjin88035@naver.com</t>
+          <t>atsing427@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0507-1306-5661</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 화원로2길 13 1층</t>
+          <t>대구광역시 달성군 현풍읍 테크노상업로 34 1층 리차드헤어샵 안</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/miyou_nail2023</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3279,17 +3279,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3298,17 +3298,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1025452354</t>
+          <t>1953875264</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1025452354</t>
+          <t>https://m.place.naver.com/place/1953875264</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3320,29 +3320,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>겸,네일</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>mneilacademy@naver.com</t>
-        </is>
-      </c>
+          <t>양고은 네일&amp;뷰티 아카데미</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0507-1442-0376</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노상업로 108 205호</t>
+          <t>대구광역시 달성군 다사읍 서재로12길 38 에코폴리스 동화아이위시 1차상가 양고은 네일&amp;뷰티 아칻</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/ho_nail0999</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3352,7 +3344,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3368,22 +3360,22 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3392,17 +3384,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1747951212</t>
+          <t>1248903128</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1747951212</t>
+          <t>https://m.place.naver.com/place/1248903128</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3414,29 +3406,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>더착한네일</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>chamhanjh@naver.com</t>
-        </is>
-      </c>
+          <t>샵네일</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1322-1416</t>
+          <t>0507-1316-6657</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 죽곡1길 19 나비타워 1층 104호 더착한네일</t>
+          <t>대구광역시 달성군 현풍읍 비슬로134길 141-6</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://instagram.com/the_kind_nail_1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3446,7 +3434,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3467,17 +3455,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q33" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3486,17 +3474,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1595935829</t>
+          <t>1655717249</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1595935829</t>
+          <t>https://m.place.naver.com/place/1655717249</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3508,29 +3496,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>네일, The 예쁨</t>
+          <t>다섯손꾸락네일</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5haveagoodday@naver.com</t>
+          <t>dongee_where@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1493-0919</t>
+          <t>0507-1344-3247</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 매곡로12길 26 1층 106호</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로174길 50 301동 지하2층 A102 호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailtheyebbeum_dasa</t>
+          <t>https://www.instagram.com/5ive_fingers_</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3565,13 +3553,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3580,17 +3568,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1004489689</t>
+          <t>1967769482</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1004489689</t>
+          <t>https://m.place.naver.com/place/1967769482</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3602,25 +3590,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>네일하이</t>
+          <t>네일,또만나</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>dojulie@naver.com</t>
+          <t>deepgriep29@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1356-9059</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노북로 33-5 1층</t>
+          <t>대구광역시 달성군 구지면 국가산단북로60길 66 1층 103호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailhigh2021</t>
+          <t>https://www.instagram.com/nail_ttomanna</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3658,10 +3650,10 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3670,17 +3662,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1919866561</t>
+          <t>2071071912</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1919866561</t>
+          <t>https://m.place.naver.com/place/2071071912</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3692,30 +3684,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nail,On</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>네일, The 예쁨</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>raphaell1004@naver.com</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1446-3385</t>
+          <t>0507-1493-0919</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 구지면 과학마을로5길 45 1층</t>
+          <t>대구광역시 달성군 다사읍 매곡로12길 26 1층 106호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.on__</t>
+          <t>https://www.instagram.com/nailtheyebbeum_dasa</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3725,7 +3721,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3745,13 +3741,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="Q36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3760,17 +3756,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2080619879</t>
+          <t>1004489689</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2080619879</t>
+          <t>https://m.place.naver.com/place/1004489689</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3782,29 +3778,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>더고은네일 대구화원점</t>
+          <t>네일데이</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>thegoeunnail@naver.com</t>
+          <t>honey126@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1380-6762</t>
+          <t>0507-1385-4658</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 비슬로 2545 화원이진캐스빌상가 110동 2층 220호</t>
+          <t>대구광역시 달성군 다사읍 대실역북로4길 6 1층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thegoeunnail</t>
+          <t>https://www.instagram.com/https://www.instagram.com/nail_day_k?igsh=eGpma3JucTN6Ymp4</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3819,7 +3815,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3830,7 +3826,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3839,13 +3835,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>697</v>
+        <v>78</v>
       </c>
       <c r="Q37" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>748</v>
+        <v>79</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3854,17 +3850,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1283196595</t>
+          <t>1302571156</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1283196595</t>
+          <t>https://m.place.naver.com/place/1302571156</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3876,29 +3872,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>다섯손꾸락네일</t>
+          <t>수이네일 다사대실역점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>dongee_where@naver.com</t>
+          <t>sweets0101@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1344-3247</t>
+          <t>0507-1423-4145</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로174길 50 301동 지하2층 A102 호</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로174길 50 죽곡협성휴포레 상가 301동 105호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/5ive_fingers_</t>
+          <t>https://www.instagram.com/sui.nail.shop</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3933,13 +3929,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="Q38" t="n">
         <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>3</v>
+        <v>107</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3948,17 +3944,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1967769482</t>
+          <t>1939839368</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1967769482</t>
+          <t>https://m.place.naver.com/place/1939839368</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3970,34 +3966,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>아이샵</t>
+          <t>오늘네일 다사대실점</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ishopcare@naver.com</t>
+          <t>yuri3935@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1359-7653</t>
+          <t>0507-1480-2662</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로 873 1층 아이샵</t>
+          <t>대구광역시 달성군 다사읍 대실역북로 70 1층 오늘네일</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s6hvsDAc</t>
+          <t>https://www.instagram.com/oneul_nail80</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4018,7 +4014,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4027,13 +4023,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>60</v>
+        <v>171</v>
       </c>
       <c r="Q39" t="n">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4042,17 +4038,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1616404575</t>
+          <t>1867576541</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1616404575</t>
+          <t>https://m.place.naver.com/place/1867576541</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4064,29 +4060,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>쏭쏭네일</t>
+          <t>네일안</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>sun525452@naver.com</t>
+          <t>sjnr27@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>053-611-8445</t>
+          <t>0507-1419-1224</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 현풍중앙로 36 1층</t>
+          <t>대구광역시 달성군 현풍읍 테크노중앙대로5길 15-3 1층 네일안</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sun525452</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4096,12 +4092,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4117,17 +4113,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4136,17 +4132,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>63179444</t>
+          <t>1568448625</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/63179444</t>
+          <t>https://m.place.naver.com/place/1568448625</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4158,25 +4154,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일헤몬 대구다사점</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>yooywyooyw@naver.com</t>
-        </is>
-      </c>
+          <t>공감네일</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 대실역북로 55 동화아이위시상가 301동103호</t>
+          <t>대구광역시 달성군 유가읍 테크노공원로 73 2층 공감네일</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailhemon_dasa</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4186,7 +4178,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4207,17 +4199,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P41" t="n">
         <v>11</v>
       </c>
       <c r="Q41" t="n">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="R41" t="n">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4226,17 +4218,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1440312692</t>
+          <t>1835125814</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1440312692</t>
+          <t>https://m.place.naver.com/place/1835125814</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4248,25 +4240,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>루미네일</t>
+          <t>넬스아이</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>jine_blog@naver.com</t>
+          <t>nailseye@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1447-0487</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 옥포읍 돌미상업로2길 26 1층 루미네일</t>
+          <t>대구광역시 달성군 현풍읍 현풍중앙로10길 73-1 1층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lume._.nailllll</t>
+          <t>https://blog.naver.com/nailseye</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4281,7 +4277,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4301,13 +4297,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="Q42" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="R42" t="n">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4316,17 +4312,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2070020547</t>
+          <t>1482658786</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2070020547</t>
+          <t>https://m.place.naver.com/place/1482658786</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4338,24 +4334,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>슈니네일</t>
+          <t>최은영네일</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>flower_lar@naver.com</t>
+          <t>geochanggun@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1391-4447</t>
+          <t>0507-1450-8017</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 현풍로6길 5 청춘난장 301호</t>
+          <t>대구광역시 달성군 다사읍 죽곡2길 3</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4395,13 +4391,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R43" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4410,17 +4406,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1526883475</t>
+          <t>1205170846</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1526883475</t>
+          <t>https://m.place.naver.com/place/1205170846</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4432,25 +4428,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>류블리뷰티</t>
+          <t>더고은네일 대구화원점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>kdskds4329@naver.com</t>
+          <t>thegoeunnail@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1380-6762</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 세천남로 35 제일풍경채 프라임 상가 205동 113호</t>
+          <t>대구광역시 달성군 화원읍 비슬로 2545 화원이진캐스빌상가 110동 2층 220호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/youvely_beauty</t>
+          <t>https://blog.naver.com/thegoeunnail</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4476,7 +4476,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4485,13 +4485,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>118</v>
+        <v>697</v>
       </c>
       <c r="Q44" t="n">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="R44" t="n">
-        <v>134</v>
+        <v>748</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4500,17 +4500,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1137133002</t>
+          <t>1283196595</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1137133002</t>
+          <t>https://m.place.naver.com/place/1283196595</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4522,29 +4522,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>넬스아이</t>
+          <t>블리스네일</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>nailseye@naver.com</t>
+          <t>everythingandmore_@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1447-0487</t>
+          <t>0507-1358-3759</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 현풍중앙로10길 73-1 1층</t>
+          <t>대구광역시 달성군 옥포읍 돌미로 70 대성베르힐 4단지 동문상가 3층 303호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailseye</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4554,12 +4554,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4575,17 +4575,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>116</v>
+        <v>12</v>
       </c>
       <c r="Q45" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="R45" t="n">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4594,17 +4594,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1482658786</t>
+          <t>1427642953</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1482658786</t>
+          <t>https://m.place.naver.com/place/1427642953</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4616,29 +4616,25 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>제이네일&amp;뷰티</t>
+          <t>네일하이</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>bomi0306@naver.com</t>
+          <t>dojulie@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0507-1435-0221</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 대실역남로2길 8-6 J:Nail&amp;beauty</t>
+          <t>대구광역시 달성군 현풍읍 테크노북로 33-5 1층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>http://instagram.com/jnail0221</t>
+          <t>https://www.instagram.com/nailhigh2021</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4673,13 +4669,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>233</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R46" t="n">
-        <v>233</v>
+        <v>3</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4688,17 +4684,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1167804147</t>
+          <t>1919866561</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1167804147</t>
+          <t>https://m.place.naver.com/place/1919866561</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4710,29 +4706,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>심쿵뷰티</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>pselll@naver.com</t>
-        </is>
-      </c>
+          <t>부베니르 네일</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1356-4777</t>
+          <t>0507-1414-4481</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노북로 260 애비뉴스완상가 1103호</t>
+          <t>대구광역시 달성군 화원읍 화암로 69 명곡시장 안 할매국밥 옆쪽</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/vous_benir_nail/</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4742,7 +4734,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4763,17 +4755,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>59</v>
+        <v>525</v>
       </c>
       <c r="Q47" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="R47" t="n">
-        <v>63</v>
+        <v>571</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4782,17 +4774,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1422631134</t>
+          <t>1474593561</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1422631134</t>
+          <t>https://m.place.naver.com/place/1474593561</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4804,29 +4796,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>네일리영</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2090063@naver.com</t>
-        </is>
-      </c>
+          <t>뷰티플랏</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1375-4992</t>
+          <t>0507-1333-4551</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노상업로 68 센텀타워1층 후면 네일리영</t>
+          <t>대구광역시 달성군 구지면 과학마을로 51-1 뷰티플랏</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naily_yeong</t>
+          <t>http://instagram.com/beauty_plot</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4861,13 +4849,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="Q48" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="R48" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4876,17 +4864,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1456853511</t>
+          <t>1623449679</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1456853511</t>
+          <t>https://m.place.naver.com/place/1623449679</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4898,29 +4886,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>샵네일</t>
+          <t>모이제이뷰티 현풍테크노폴리스점</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>tiger9313@naver.com</t>
+          <t>wheend@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1316-6657</t>
+          <t>0507-1446-0309</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 비슬로134길 141-6</t>
+          <t>대구광역시 달성군 유가읍 테크노중앙대로 240 한라하우젠트 2층 209호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/moi.j_beauty</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4930,7 +4918,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4951,17 +4939,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>14</v>
+        <v>312</v>
       </c>
       <c r="Q49" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="R49" t="n">
-        <v>15</v>
+        <v>327</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -4970,17 +4958,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1655717249</t>
+          <t>1161931493</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1655717249</t>
+          <t>https://m.place.naver.com/place/1161931493</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4992,34 +4980,30 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>뷰티에디트</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>jyhwang317@naver.com</t>
-        </is>
-      </c>
+          <t>채채네일</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1381-3093</t>
+          <t>0507-1361-6446</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노상업로 52 201호</t>
+          <t>대구광역시 달성군 유가읍 테크노중앙대로6길 16-10 1층 103호 채채네일</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_by_sj</t>
+          <t>https://open.kakao.com/o/sChJDaCh</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5040,7 +5024,7 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5049,13 +5033,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>211</v>
+        <v>115</v>
       </c>
       <c r="Q50" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>218</v>
+        <v>115</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5064,17 +5048,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1651900268</t>
+          <t>2031524021</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1651900268</t>
+          <t>https://m.place.naver.com/place/2031524021</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5086,29 +5070,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>임블리제네일</t>
+          <t>네일 봄</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>j333ok@naver.com</t>
+          <t>joolijooli@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1329-2089</t>
+          <t>0507-1306-6012</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 옥포읍 돌미로2길 18 임블리제</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로 875 MA프라자 105호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/imblige</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5118,7 +5102,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5139,17 +5123,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R51" t="n">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5158,17 +5142,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1446451273</t>
+          <t>1419253509</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1446451273</t>
+          <t>https://m.place.naver.com/place/1419253509</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5180,25 +5164,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>W뷰티</t>
+          <t>예쁘다니손</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>wbeautykorea@naver.com</t>
+          <t>rhdwn910@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>053-582-4141</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 서재로 140 1층</t>
+          <t>대구광역시 달성군 다사읍 세천로 160</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>http://instagram.com/w_beauty777</t>
+          <t>http://www.instagram.com/_y_s2</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5224,7 +5212,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5233,13 +5221,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="R52" t="n">
-        <v>4</v>
+        <v>170</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5248,17 +5236,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1781318151</t>
+          <t>1241226738</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1781318151</t>
+          <t>https://m.place.naver.com/place/1241226738</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5270,24 +5258,24 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>지니네일</t>
+          <t>네일을,이쁘게</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>goto_seoul@naver.com</t>
+          <t>gold77com@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1389-4020</t>
+          <t>0507-1317-3565</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 옥포읍 비슬로447길 11 달성삼환나우빌 301동 102호</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로 881 1층.107호 네일은,이쁘게</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5327,13 +5315,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5342,17 +5330,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1621609186</t>
+          <t>1456297687</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1621609186</t>
+          <t>https://m.place.naver.com/place/1456297687</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5364,29 +5352,25 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>솜솜네일</t>
+          <t>뷰티박스</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>mydbfla33@naver.com</t>
+          <t>dasom4343@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0507-1384-9259</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 현풍로47길 67 화이트캐슬 101호</t>
+          <t>대구광역시 달성군 다사읍 세천로 182-10 현대 썬앤빌상가 302동 104호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/somsom.nail2</t>
+          <t>https://www.instagram.com/beauty__box_j</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5421,13 +5405,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="R54" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5436,17 +5420,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1791561455</t>
+          <t>1149958107</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1791561455</t>
+          <t>https://m.place.naver.com/place/1149958107</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5458,29 +5442,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>미니네일</t>
+          <t>루미네일</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mymomy1202@naver.com</t>
+          <t>jine_blog@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>0507-1427-0344</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노중앙대로 243 1층 118호(타임스퀘어)</t>
+          <t>대구광역시 달성군 옥포읍 돌미상업로2길 26 1층 루미네일</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mini.nail0101</t>
+          <t>https://www.instagram.com/lume._.nailllll</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5515,13 +5495,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="Q55" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="R55" t="n">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5530,17 +5510,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1657933953</t>
+          <t>2070020547</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1657933953</t>
+          <t>https://m.place.naver.com/place/2070020547</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5552,29 +5532,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>미자네일</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>misajayeon@naver.com</t>
-        </is>
-      </c>
+          <t>벨라부띠끄</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>053-583-7282</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 서재로7길 25 동화아이위시3차 상가602동 107호</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로 874 벨라부띠끄</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/bellaboutique.nail</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5584,7 +5556,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5605,17 +5577,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="Q56" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R56" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5624,17 +5596,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>20771150</t>
+          <t>1192828282</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20771150</t>
+          <t>https://m.place.naver.com/place/1192828282</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5646,12 +5618,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>네일또와</t>
+          <t>네일 예쁘다</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>sj330035@naver.com</t>
+          <t>yooky617@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -5659,7 +5631,7 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노상업로 26 108호</t>
+          <t>대구광역시 달성군 유가읍 테크노상업로 108 2층 205호 네일예쁘다</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5699,13 +5671,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5714,17 +5686,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>2002873448</t>
+          <t>1252953982</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2002873448</t>
+          <t>https://m.place.naver.com/place/1252953982</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5736,29 +5708,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>네일트렌드제이 다사대실역점</t>
+          <t>디오르뷰티</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>happy_y119@naver.com</t>
+          <t>kangvely224@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>0507-1365-1789</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로 878 2층 (설빙 옆)</t>
+          <t>대구광역시 달성군 유가읍 테크노북로 260 201동 1124호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://linktr.ee/nailtrendj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5768,7 +5736,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5784,7 +5752,7 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5793,13 +5761,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>473</v>
+        <v>29</v>
       </c>
       <c r="Q58" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>565</v>
+        <v>29</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5808,17 +5776,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>21607795</t>
+          <t>1978929871</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21607795</t>
+          <t>https://m.place.naver.com/place/1978929871</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5830,29 +5798,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>예쁘다니손</t>
+          <t>미니네일</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>rhdwn910@naver.com</t>
+          <t>mymomy1202@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>053-582-4141</t>
+          <t>0507-1427-0344</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 세천로 160</t>
+          <t>대구광역시 달성군 현풍읍 테크노중앙대로 243 1층 118호(타임스퀘어)</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/_y_s2</t>
+          <t>https://www.instagram.com/mini.nail0101</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5878,7 +5846,7 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5887,13 +5855,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>146</v>
+        <v>6</v>
       </c>
       <c r="R59" t="n">
-        <v>170</v>
+        <v>7</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5902,17 +5870,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1241226738</t>
+          <t>1657933953</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1241226738</t>
+          <t>https://m.place.naver.com/place/1657933953</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5924,29 +5892,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>네일데이</t>
+          <t>현네일앤뷰티</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>honey126@naver.com</t>
+          <t>lovelyddu1@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0507-1385-4658</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 대실역북로4길 6 1층</t>
+          <t>대구광역시 달성군 화원읍 인흥길 83 1층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/https://www.instagram.com/nail_day_k?igsh=eGpma3JucTN6Ymp4</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5956,7 +5920,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5977,17 +5941,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="Q60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -5996,17 +5960,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1302571156</t>
+          <t>1094979616</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1302571156</t>
+          <t>https://m.place.naver.com/place/1094979616</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6018,29 +5982,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>네일티라노 현풍</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>puri12@naver.com</t>
-        </is>
-      </c>
+          <t>다비드네일&amp;래쉬 현풍테크노폴리스점</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1364-3106</t>
+          <t>0507-1403-0548</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노중앙대로 240 한라하우젠트 상가 1층 120호</t>
+          <t>대구광역시 달성군 유가읍 테크노북로 260 더예미지센트럴 201동 2층 2131호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_DIXNK/friend</t>
+          <t>http://pf.kakao.com/_vlDqG</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6075,13 +6035,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="Q61" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="R61" t="n">
-        <v>152</v>
+        <v>88</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6090,17 +6050,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1340647385</t>
+          <t>1764976820</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1340647385</t>
+          <t>https://m.place.naver.com/place/1764976820</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6112,29 +6072,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>룩네일</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>4chi_27@naver.com</t>
-        </is>
-      </c>
+          <t>네일반하다</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1307-5776</t>
+          <t>0507-1320-7016</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 옥포읍 돌미로 50 2층 201호</t>
+          <t>대구광역시 달성군 유가읍 테크노순환로 423 중흥S클래스 아파트 상가 2층 203호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>http://instagram.com/Lo_oknail</t>
+          <t>https://www.instagram.com/yoomi_nail_banhada</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6169,13 +6125,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R62" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6184,17 +6140,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1257117862</t>
+          <t>1903028426</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1257117862</t>
+          <t>https://m.place.naver.com/place/1903028426</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6206,29 +6162,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>샤네일</t>
+          <t>모란네일&amp;속눈썹 구지본점</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>jgy5220@naver.com</t>
+          <t>aszx5439@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1461-4143</t>
+          <t>0507-1402-3393</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 옥포읍 돌미상업로 10 1층 109호</t>
+          <t>대구광역시 달성군 구지면 국가산단북로34길 10 131동 1층 112호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>http://instagram.com/chanail_4141</t>
+          <t>https://www.instagram.com/peonynail02</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6263,13 +6219,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="Q63" t="n">
         <v>1</v>
       </c>
       <c r="R63" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6278,17 +6234,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1477126656</t>
+          <t>1710361565</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1477126656</t>
+          <t>https://m.place.naver.com/place/1710361565</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6300,29 +6256,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>제이뷰티</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>ggaau0073@naver.com</t>
-        </is>
-      </c>
+          <t>미자네일</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1384-1216</t>
+          <t>053-583-7282</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 구지면 국가산단대로70길 42 상가 1호</t>
+          <t>대구광역시 달성군 다사읍 서재로7길 25 동화아이위시3차 상가602동 107호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/j_beauty_010.4931.1212</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6332,7 +6284,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6353,17 +6305,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6372,17 +6324,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1507035488</t>
+          <t>20771150</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1507035488</t>
+          <t>https://m.place.naver.com/place/20771150</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6394,24 +6346,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>딸기네일</t>
+          <t>네일살롱</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>aquawhta@naver.com</t>
+          <t>wing3527@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1403-7930</t>
+          <t>053-615-6667</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노중앙대로5길 15-7</t>
+          <t>대구광역시 달성군 논공읍 논공로9길 79-6</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6451,13 +6403,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R65" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6466,17 +6418,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1532741745</t>
+          <t>1596046698</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1532741745</t>
+          <t>https://m.place.naver.com/place/1596046698</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6488,29 +6440,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>모이제이뷰티 현풍테크노폴리스점</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>wheend@naver.com</t>
-        </is>
-      </c>
+          <t>꾸밈네일</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>0507-1446-0309</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노중앙대로 240 한라하우젠트 2층 209호</t>
+          <t>대구광역시 달성군 다사읍 서재로30길 17 보성1차상가 101호 꾸밈네일</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>http://instagram.com/moi.j_beauty</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6520,7 +6464,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6541,17 +6485,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>312</v>
+        <v>2</v>
       </c>
       <c r="Q66" t="n">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="R66" t="n">
-        <v>327</v>
+        <v>63</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6560,17 +6504,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1161931493</t>
+          <t>706872304</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161931493</t>
+          <t>https://m.place.naver.com/place/706872304</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6582,34 +6526,30 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네일,새벽</t>
+          <t>샵손톱에물들다화원</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>chelba789@naver.com</t>
+          <t>wldms141300@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>0507-1309-4166</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노북로 260 201동 1층 1121호</t>
+          <t>대구광역시 달성군 화원읍 화원로1길 46-11 1층</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_XSGUG</t>
+          <t>https://blog.naver.com/wldms141300</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6619,7 +6559,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6630,22 +6570,22 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="Q67" t="n">
-        <v>3</v>
+        <v>315</v>
       </c>
       <c r="R67" t="n">
-        <v>43</v>
+        <v>335</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6654,17 +6594,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1298520181</t>
+          <t>1840469863</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1298520181</t>
+          <t>https://m.place.naver.com/place/1840469863</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6676,39 +6616,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>네일스토리</t>
+          <t>코지무이</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>yeju0414@naver.com</t>
+          <t>dydanss@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>053-585-3646</t>
+          <t>0507-1301-4534</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 서재로7길 25 동화아이위시 3차 상가 2층 601동 203호</t>
+          <t>대구광역시 달성군 다사읍 대실역남로2길 8-5 1층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_pGxhus</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6724,7 +6664,7 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6733,10 +6673,10 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Q68" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R68" t="n">
         <v>11</v>
@@ -6748,17 +6688,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>36208505</t>
+          <t>1306738999</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36208505</t>
+          <t>https://m.place.naver.com/place/1306738999</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6770,29 +6710,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>네일플랏</t>
+          <t>더착한네일</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>jinnny89@naver.com</t>
+          <t>chamhanjh@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1406-2529</t>
+          <t>0507-1322-1416</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 옥포읍 돌미상업로 9 화인빌딩 1층</t>
+          <t>대구광역시 달성군 다사읍 죽곡1길 19 나비타워 1층 104호 더착한네일</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_plot</t>
+          <t>https://instagram.com/the_kind_nail_1</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6827,13 +6767,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Q69" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="R69" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6842,17 +6782,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>39886025</t>
+          <t>1595935829</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/39886025</t>
+          <t>https://m.place.naver.com/place/1595935829</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6864,24 +6804,20 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>석네일 뷰티</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>heesun0077@naver.com</t>
-        </is>
-      </c>
+          <t>슈니네일</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1383-4045</t>
+          <t>0507-1391-4447</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 세천본길 45-8 1층 석네일뷰티</t>
+          <t>대구광역시 달성군 현풍읍 현풍로6길 5 청춘난장 301호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6921,13 +6857,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q70" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R70" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6936,17 +6872,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1784441305</t>
+          <t>1526883475</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1784441305</t>
+          <t>https://m.place.naver.com/place/1526883475</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6958,24 +6894,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>네일의 온도</t>
+          <t>석네일 뷰티</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>mistymoon5@naver.com</t>
+          <t>heesun0077@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1346-1171</t>
+          <t>0507-1383-4045</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 세천로 146 1층 102-1호, 네일의온도</t>
+          <t>대구광역시 달성군 다사읍 세천본길 45-8 1층 석네일뷰티</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7018,10 +6954,10 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7030,17 +6966,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>2090742652</t>
+          <t>1784441305</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2090742652</t>
+          <t>https://m.place.naver.com/place/1784441305</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7052,34 +6988,30 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>다비드네일&amp;래쉬 현풍테크노폴리스점</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>mipnu3503@naver.com</t>
-        </is>
-      </c>
+          <t>Nail,On</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1403-0548</t>
+          <t>0507-1446-3385</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노북로 260 더예미지센트럴 201동 2층 2131호</t>
+          <t>대구광역시 달성군 구지면 과학마을로5길 45 1층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_vlDqG</t>
+          <t>https://www.instagram.com/nail.on__</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7100,7 +7032,7 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7109,13 +7041,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="Q72" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="R72" t="n">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7124,17 +7056,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1764976820</t>
+          <t>2080619879</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1764976820</t>
+          <t>https://m.place.naver.com/place/2080619879</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7146,25 +7078,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>네일을, 이쁘게</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>loosetime@naver.com</t>
-        </is>
-      </c>
+          <t>더착한네일 2호점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로 881 1층 107호</t>
+          <t>대구광역시 달성군 다사읍 세천로 108 앙코르라구나 2층 더착한네일</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pretty_nai1_</t>
+          <t>http://instagram.com/the_kind_nail2</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7199,13 +7127,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>160</v>
+        <v>10</v>
       </c>
       <c r="Q73" t="n">
-        <v>2</v>
+        <v>89</v>
       </c>
       <c r="R73" t="n">
-        <v>162</v>
+        <v>99</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7214,17 +7142,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1822297833</t>
+          <t>1959040418</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1822297833</t>
+          <t>https://m.place.naver.com/place/1959040418</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7236,29 +7164,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>진네일</t>
+          <t>솜솜네일</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>jin_nail6453@naver.com</t>
+          <t>mydbfla33@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1333-6453</t>
+          <t>0507-1384-9259</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노공원로 17 벨류스퀘어1층113호 진네일</t>
+          <t>대구광역시 달성군 유가읍 현풍로47길 67 화이트캐슬 101호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jin_nail6453</t>
+          <t>https://www.instagram.com/somsom.nail2</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7293,13 +7221,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="Q74" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="R74" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7308,17 +7236,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1289979524</t>
+          <t>1791561455</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1289979524</t>
+          <t>https://m.place.naver.com/place/1791561455</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7330,30 +7258,34 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>벨라부띠끄</t>
+          <t>레비라네일 현풍테크노폴리스점</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>y77777k@naver.com</t>
+          <t>apple6931@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1430-5033</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로 874 벨라부띠끄</t>
+          <t>대구광역시 달성군 유가읍 테크노북로 260 예미지상가 2171호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>http://instagram.com/bellaboutique.nail</t>
+          <t>http://pf.kakao.com/_YJxhxlG</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7374,7 +7306,7 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7383,13 +7315,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>52</v>
+        <v>155</v>
       </c>
       <c r="Q75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R75" t="n">
-        <v>57</v>
+        <v>159</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7398,17 +7330,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1192828282</t>
+          <t>1808169841</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1192828282</t>
+          <t>https://m.place.naver.com/place/1808169841</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7420,29 +7352,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>부베니르 네일</t>
+          <t>제이뷰티</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>bliss_322@naver.com</t>
+          <t>nanamoon23@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1414-4481</t>
+          <t>0507-1384-1216</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 화암로 69 명곡시장 안 할매국밥 옆쪽</t>
+          <t>대구광역시 달성군 구지면 국가산단대로70길 42 상가 1호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/vous_benir_nail/</t>
+          <t>https://www.instagram.com/j_beauty_010.4931.1212</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7477,13 +7409,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>525</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="R76" t="n">
-        <v>571</v>
+        <v>4</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7492,17 +7424,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1474593561</t>
+          <t>1507035488</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1474593561</t>
+          <t>https://m.place.naver.com/place/1507035488</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7514,29 +7446,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>엄지공주뷰티샵</t>
+          <t>홀드풋케어 발톱무좀 내성발톱 문제성발관리</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>tosemdnlcl@naver.com</t>
+          <t>bi1142@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1358-0830</t>
+          <t>070-4866-1122</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 명곡로 9 명곡미래빌1단지 상가 2층</t>
+          <t>대구광역시 달성군 유가읍 테크노북로 260 201동 2200호</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tosemdnlcl</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7546,12 +7478,12 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -7567,17 +7499,17 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="Q77" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R77" t="n">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7586,17 +7518,17 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>20061778</t>
+          <t>1280044307</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20061778</t>
+          <t>https://m.place.naver.com/place/1280044307</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7608,29 +7540,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>최은영네일</t>
+          <t>네일써니</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>geochanggun@naver.com</t>
+          <t>ha780106@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0507-1450-8017</t>
+          <t>0507-1410-7991</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 죽곡2길 3</t>
+          <t>대구광역시 달성군 화원읍 비슬로 2545 상가 110동 3층 310호</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail.sunny7985</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7640,7 +7572,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7661,17 +7593,17 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P78" t="n">
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="R78" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7680,17 +7612,17 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1205170846</t>
+          <t>1704201083</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1205170846</t>
+          <t>https://m.place.naver.com/place/1704201083</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7702,29 +7634,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>네일반하다</t>
+          <t>으니네일</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>iiijuheeiii@naver.com</t>
+          <t>gost5544@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0507-1320-7016</t>
+          <t>0507-1385-1093</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노순환로 423 중흥S클래스 아파트 상가 2층 203호</t>
+          <t>대구광역시 달성군 다사읍 달구벌대로174길 21 2층</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yoomi_nail_banhada</t>
+          <t>https://www.instagram.com/euni__nail</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7762,10 +7694,10 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7774,17 +7706,17 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1903028426</t>
+          <t>1662155594</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1903028426</t>
+          <t>https://m.place.naver.com/place/1662155594</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7796,29 +7728,25 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>뷰티플랏</t>
+          <t>네일헤몬 대구다사점</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>123ggo@naver.com</t>
+          <t>yooywyooyw@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>0507-1333-4551</t>
-        </is>
-      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 구지면 과학마을로 51-1 뷰티플랏</t>
+          <t>대구광역시 달성군 다사읍 대실역북로 55 동화아이위시상가 301동103호</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>http://instagram.com/beauty_plot</t>
+          <t>https://www.instagram.com/nailhemon_dasa</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7853,13 +7781,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q80" t="n">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="R80" t="n">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7868,17 +7796,17 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>1623449679</t>
+          <t>1440312692</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1623449679</t>
+          <t>https://m.place.naver.com/place/1440312692</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7890,29 +7818,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>바르다네일</t>
+          <t>네일티라노 현풍</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>seolaj@naver.com</t>
+          <t>puri12@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0507-1317-7634</t>
+          <t>0507-1364-3106</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 대실역남로 34 1층 106호</t>
+          <t>대구광역시 달성군 유가읍 테크노중앙대로 240 한라하우젠트 상가 1층 120호</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/CgmM1uHLvC_/?igshid=YmMyMTA2M2Y=</t>
+          <t>http://pf.kakao.com/_DIXNK/friend</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7927,7 +7855,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -7938,7 +7866,7 @@
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -7947,13 +7875,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="Q81" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R81" t="n">
-        <v>16</v>
+        <v>153</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -7962,17 +7890,17 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1585213142</t>
+          <t>1340647385</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1585213142</t>
+          <t>https://m.place.naver.com/place/1340647385</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7984,29 +7912,25 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>네일,또만나</t>
+          <t>류블리뷰티</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>deepgriep29@naver.com</t>
+          <t>kdskds4329@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>0507-1356-9059</t>
-        </is>
-      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 구지면 국가산단북로60길 66 1층 103호</t>
+          <t>대구광역시 달성군 다사읍 세천남로 35 제일풍경채 프라임 상가 205동 113호</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ttomanna</t>
+          <t>https://www.instagram.com/youvely_beauty</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8041,13 +7965,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R82" t="n">
-        <v>1</v>
+        <v>134</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8056,17 +7980,17 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>2071071912</t>
+          <t>1137133002</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2071071912</t>
+          <t>https://m.place.naver.com/place/1137133002</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8078,34 +8002,34 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>코지무이</t>
+          <t>뷰티해요</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>banglang93@naver.com</t>
+          <t>bonita5332@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0507-1301-4534</t>
+          <t>0507-1336-7045</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 대실역남로2길 8-5 1층</t>
+          <t>대구광역시 달성군 다사읍 대실역북로 12 301호</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pGxhus</t>
+          <t>https://blog.naver.com/bonita5332</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8115,7 +8039,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8126,22 +8050,22 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>4</v>
+        <v>93</v>
       </c>
       <c r="Q83" t="n">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="R83" t="n">
-        <v>11</v>
+        <v>176</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8150,17 +8074,17 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1306738999</t>
+          <t>1243747619</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1306738999</t>
+          <t>https://m.place.naver.com/place/1243747619</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8172,30 +8096,34 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>더착한네일 2호점</t>
+          <t>네일,새벽</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>yujiny43@naver.com</t>
+          <t>chelba789@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0507-1309-4166</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 세천로 108 앙코르라구나 2층 더착한네일</t>
+          <t>대구광역시 달성군 유가읍 테크노북로 260 201동 1층 1121호</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>http://instagram.com/the_kind_nail2</t>
+          <t>http://pf.kakao.com/_XSGUG</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -8216,7 +8144,7 @@
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -8225,13 +8153,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="Q84" t="n">
-        <v>89</v>
+        <v>3</v>
       </c>
       <c r="R84" t="n">
-        <v>99</v>
+        <v>43</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8240,17 +8168,17 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1959040418</t>
+          <t>1298520181</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1959040418</t>
+          <t>https://m.place.naver.com/place/1298520181</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8262,29 +8190,25 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>네일살롱</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>wing3527@naver.com</t>
-        </is>
-      </c>
+          <t>네일하담</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>053-615-6667</t>
+          <t>0507-1318-5676</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 논공읍 논공로9길 79-6</t>
+          <t>대구광역시 달성군 논공읍 논공로9길 68 2층</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailhadam_</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8294,7 +8218,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -8315,7 +8239,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P85" t="n">
@@ -8334,17 +8258,17 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1596046698</t>
+          <t>1157430781</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1596046698</t>
+          <t>https://m.place.naver.com/place/1157430781</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8356,39 +8280,35 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>제이오뷰티 다사대실역점</t>
+          <t>네일또와</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>happy_y119@naver.com</t>
+          <t>sj330035@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>0507-1372-0952</t>
-        </is>
-      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로 846-1 제이오뷰티</t>
+          <t>대구광역시 달성군 현풍읍 테크노상업로 26 108호</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sc9akTld</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -8404,22 +8324,22 @@
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P86" t="n">
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8428,17 +8348,17 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1940949870</t>
+          <t>2002873448</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1940949870</t>
+          <t>https://m.place.naver.com/place/2002873448</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8450,29 +8370,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>오늘네일 다사대실점</t>
+          <t>모인뷰티</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>yuri3935@naver.com</t>
+          <t>goldminy@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1480-2662</t>
+          <t>0507-1374-7011</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 대실역북로 70 1층 오늘네일</t>
+          <t>대구광역시 달성군 화원읍 화원로1길 46-8 1층</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oneul_nail80</t>
+          <t>https://www.instagram.com/moin_beauty</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8507,13 +8427,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>171</v>
+        <v>32</v>
       </c>
       <c r="Q87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>173</v>
+        <v>32</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8522,17 +8442,17 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1867576541</t>
+          <t>1855496054</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1867576541</t>
+          <t>https://m.place.naver.com/place/1855496054</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8544,25 +8464,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>공감네일</t>
+          <t>뮤아드네일</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>finger1229@naver.com</t>
+          <t>twolee10_@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0507-1312-2226</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노공원로 73 2층 공감네일</t>
+          <t>대구광역시 달성군 현풍읍 테크노중앙대로5길 15-9 1층 101호</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/muad.nail</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8572,7 +8496,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -8593,17 +8517,17 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Q88" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R88" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8612,17 +8536,17 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1835125814</t>
+          <t>2002612318</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835125814</t>
+          <t>https://m.place.naver.com/place/2002612318</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8634,30 +8558,34 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>샵손톱에물들다화원</t>
+          <t>몽디네일 현풍테크노폴리스점</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>wldms141300@naver.com</t>
+          <t>chelba789@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0507-1358-9310</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 화원읍 화원로1길 46-11 1층</t>
+          <t>대구광역시 달성군 유가읍 테크노중앙대로6길 16-6 1층 몽디네일</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wldms141300</t>
+          <t>http://pf.kakao.com/_bXNxkG</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -8667,7 +8595,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -8678,22 +8606,22 @@
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="Q89" t="n">
-        <v>315</v>
+        <v>8</v>
       </c>
       <c r="R89" t="n">
-        <v>335</v>
+        <v>163</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8702,17 +8630,17 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1840469863</t>
+          <t>1572731285</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1840469863</t>
+          <t>https://m.place.naver.com/place/1572731285</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8724,29 +8652,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>남자다운네일</t>
+          <t>심쿵뷰티</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>kfood011@naver.com</t>
+          <t>pselll@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>053-582-7676</t>
+          <t>0507-1356-4777</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 세천북로 13</t>
+          <t>대구광역시 달성군 유가읍 테크노북로 260 애비뉴스완상가 1103호</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kfood011</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8756,12 +8684,12 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -8781,13 +8709,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="Q90" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="R90" t="n">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8796,17 +8724,17 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>218033600</t>
+          <t>1422631134</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/218033600</t>
+          <t>https://m.place.naver.com/place/1422631134</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8818,25 +8746,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>뷰티박스</t>
+          <t>네일플랏</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>dasom4343@naver.com</t>
+          <t>jinnny89@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0507-1406-2529</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 세천로 182-10 현대 썬앤빌상가 302동 104호</t>
+          <t>대구광역시 달성군 옥포읍 돌미상업로 9 화인빌딩 1층</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beauty__box_j</t>
+          <t>http://instagram.com/nail_plot</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8871,13 +8803,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q91" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="R91" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8886,17 +8818,17 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1149958107</t>
+          <t>39886025</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1149958107</t>
+          <t>https://m.place.naver.com/place/39886025</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8908,24 +8840,16 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>모브네일</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>jaera423@naver.com</t>
-        </is>
-      </c>
+          <t>스페이스 블링</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>0507-1327-7428</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 구지면 국가산단대로70길 17 대구국가산단디에트르더센트럴 상가 111호</t>
+          <t>대구광역시 달성군 유가읍 테크노북로 260 2층 2164호(예미지 상가)</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -8965,13 +8889,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>3</v>
+        <v>175</v>
       </c>
       <c r="Q92" t="n">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="R92" t="n">
-        <v>8</v>
+        <v>232</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -8980,17 +8904,17 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1135244635</t>
+          <t>2080831582</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1135244635</t>
+          <t>https://m.place.naver.com/place/2080831582</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9002,34 +8926,34 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>채채네일</t>
+          <t>네일하이</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>aromi486kr@naver.com</t>
+          <t>dojulie@naver.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>0507-1361-6446</t>
+          <t>0507-1324-1002</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노중앙대로6길 16-10 1층 103호 채채네일</t>
+          <t>대구광역시 달성군 다사읍 다사역로 60 다사역 이편한세상 상가 101호</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sChJDaCh</t>
+          <t>https://www.instagram.com/nailhi__dasa</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -9050,7 +8974,7 @@
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -9059,13 +8983,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>115</v>
+        <v>2</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R93" t="n">
-        <v>115</v>
+        <v>5</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -9074,17 +8998,17 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>2031524021</t>
+          <t>2061866805</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2031524021</t>
+          <t>https://m.place.naver.com/place/2061866805</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9096,24 +9020,24 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>네일안</t>
+          <t>걸스네일샵</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>sjnr27@naver.com</t>
+          <t>charlotte0522@naver.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0507-1419-1224</t>
+          <t>053-615-4121</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노중앙대로5길 15-3 1층 네일안</t>
+          <t>대구광역시 달성군 현풍읍 테크노중앙대로5길 33-15</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -9153,13 +9077,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9168,17 +9092,17 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>1568448625</t>
+          <t>1429747999</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1568448625</t>
+          <t>https://m.place.naver.com/place/1429747999</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9190,29 +9114,25 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>맘스네일 현풍점</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>j_hee_2@naver.com</t>
-        </is>
-      </c>
+          <t>네일누림 현풍테크노폴리스점</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0507-1334-7625</t>
+          <t>0507-1489-4282</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노중앙대로 326-27 1층</t>
+          <t>대구광역시 달성군 유가읍 테크노상업로 111 테크노폴리스4단지 상가동 1층 105호</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hyunpung_momsnail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9222,7 +9142,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -9243,17 +9163,17 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>231</v>
+        <v>107</v>
       </c>
       <c r="Q95" t="n">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="R95" t="n">
-        <v>289</v>
+        <v>111</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -9262,17 +9182,17 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>1058493414</t>
+          <t>1028594389</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1058493414</t>
+          <t>https://m.place.naver.com/place/1028594389</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9284,39 +9204,35 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>몽디네일 현풍테크노폴리스점</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>chelba789@naver.com</t>
-        </is>
-      </c>
+          <t>반짝반짝네일</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0507-1358-9310</t>
+          <t>053-581-0210</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노중앙대로6길 16-6 1층 몽디네일</t>
+          <t>대구광역시 달성군 다사읍 서재본길 10 1층 101호</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_bXNxkG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -9332,22 +9248,22 @@
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="Q96" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="R96" t="n">
-        <v>163</v>
+        <v>16</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -9356,17 +9272,17 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>1572731285</t>
+          <t>1571722665</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1572731285</t>
+          <t>https://m.place.naver.com/place/1571722665</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9378,20 +9294,16 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>디오르뷰티</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>kangvely224@naver.com</t>
-        </is>
-      </c>
+          <t>네일샵</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노북로 260 201동 1124호</t>
+          <t>대구광역시 달성군 화원읍 화원로 29</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9431,13 +9343,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R97" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -9446,17 +9358,17 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>1978929871</t>
+          <t>1210929171</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1978929871</t>
+          <t>https://m.place.naver.com/place/1210929171</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9468,29 +9380,25 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>모란네일&amp;속눈썹 구지본점</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>aszx5439@naver.com</t>
-        </is>
-      </c>
+          <t>네일스토리</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0507-1402-3393</t>
+          <t>053-585-3646</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 구지면 국가산단북로34길 10 131동 1층 112호</t>
+          <t>대구광역시 달성군 다사읍 서재로7길 25 동화아이위시 3차 상가 2층 601동 203호</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/peonynail02</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -9500,7 +9408,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -9521,17 +9429,17 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="Q98" t="n">
         <v>1</v>
       </c>
       <c r="R98" t="n">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -9540,17 +9448,17 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>1710361565</t>
+          <t>36208505</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1710361565</t>
+          <t>https://m.place.naver.com/place/36208505</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9562,29 +9470,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>네일하이</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>dojulie@naver.com</t>
-        </is>
-      </c>
+          <t>오늘도네일</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>0507-1324-1002</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 다사역로 60 다사역 이편한세상 상가 101호</t>
+          <t>대구광역시 달성군 구지면 과학마을로3길 15 1층</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailhi__dasa</t>
+          <t>https://www.instagram.com/oneuldo__nail/</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -9619,10 +9519,10 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R99" t="n">
         <v>5</v>
@@ -9634,17 +9534,17 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>2061866805</t>
+          <t>1331774074</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2061866805</t>
+          <t>https://m.place.naver.com/place/1331774074</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9656,40 +9556,44 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>네일 예쁘다</t>
+          <t>바르다네일</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>yooky617@naver.com</t>
+          <t>seolaj@naver.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>0507-1317-7634</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 유가읍 테크노상업로 108 2층 205호 네일예쁘다</t>
+          <t>대구광역시 달성군 다사읍 대실역남로 34 1층 106호</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/p/CgmM1uHLvC_/?igshid=YmMyMTA2M2Y=</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -9705,17 +9609,17 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P100" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R100" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -9724,17 +9628,17 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>1252953982</t>
+          <t>1585213142</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1252953982</t>
+          <t>https://m.place.naver.com/place/1585213142</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9746,24 +9650,24 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>걸스네일샵</t>
+          <t>딸기네일</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>thwjd91070@naver.com</t>
+          <t>aquawhta@naver.com</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>053-615-4121</t>
+          <t>0507-1403-7930</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 현풍읍 테크노중앙대로5길 33-15</t>
+          <t>대구광역시 달성군 현풍읍 테크노중앙대로5길 15-7</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -9803,13 +9707,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -9818,17 +9722,17 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>1429747999</t>
+          <t>1532741745</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1429747999</t>
+          <t>https://m.place.naver.com/place/1532741745</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9840,29 +9744,25 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>꼼네일</t>
+          <t>욜로네일</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>immire@naver.com</t>
+          <t>s2s20228@naver.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>0507-1334-1563</t>
-        </is>
-      </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 다사읍 달구벌대로174길 50 303호</t>
+          <t>대구광역시 달성군 옥포읍 돌미로2길 6</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kkom_nail21</t>
+          <t>http://instagram.com/yolonail9010</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9897,13 +9797,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q102" t="n">
         <v>1</v>
       </c>
       <c r="R102" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -9912,17 +9812,17 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>1113405538</t>
+          <t>1935910413</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1113405538</t>
+          <t>https://m.place.naver.com/place/1935910413</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9934,39 +9834,35 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>정민뷰티</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>ckchungkang@naver.com</t>
-        </is>
-      </c>
+          <t>겸,네일</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>0507-1325-7846</t>
+          <t>0507-1442-0376</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>대구광역시 달성군 구지면 과학마을로2길 71 1층</t>
+          <t>대구광역시 달성군 유가읍 테크노상업로 108 205호</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://cafe.naver.com/jastyle</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -9987,17 +9883,17 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -10006,17 +9902,17 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>1739070946</t>
+          <t>1747951212</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1739070946</t>
+          <t>https://m.place.naver.com/place/1747951212</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10084,10 +9980,10 @@
         <v>8</v>
       </c>
       <c r="Q104" t="n">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="R104" t="n">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -10106,7 +10002,7 @@
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
